--- a/बजेट माग estimate/नगर बजेट estimate/malsim khanepaani/valuation malsim khanepaani.xlsx
+++ b/बजेट माग estimate/नगर बजेट estimate/malsim khanepaani/valuation malsim khanepaani.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11B7F6CB-9C1A-4FB9-9125-FA9D4F431996}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1A6DE53-57E7-4238-B20B-08EC16B7A709}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="estimate" sheetId="12" r:id="rId1"/>
     <sheet name="WCR" sheetId="14" r:id="rId2"/>
     <sheet name="V" sheetId="13" r:id="rId3"/>
-    <sheet name="original estimate" sheetId="15" state="hidden" r:id="rId4"/>
+    <sheet name="M" sheetId="16" r:id="rId4"/>
+    <sheet name="original estimate" sheetId="15" state="hidden" r:id="rId5"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId5"/>
     <externalReference r:id="rId6"/>
     <externalReference r:id="rId7"/>
     <externalReference r:id="rId8"/>
@@ -27,6 +27,7 @@
     <definedName name="description_103">[1]Abstract!$B$16</definedName>
     <definedName name="description_124" localSheetId="0">#REF!</definedName>
     <definedName name="description_124" localSheetId="3">#REF!</definedName>
+    <definedName name="description_124" localSheetId="4">#REF!</definedName>
     <definedName name="description_124" localSheetId="2">#REF!</definedName>
     <definedName name="description_124" localSheetId="1">#REF!</definedName>
     <definedName name="description_124">#REF!</definedName>
@@ -38,34 +39,40 @@
     <definedName name="description_3">[1]Abstract!$B$169</definedName>
     <definedName name="description_310" localSheetId="0">#REF!</definedName>
     <definedName name="description_310" localSheetId="3">#REF!</definedName>
+    <definedName name="description_310" localSheetId="4">#REF!</definedName>
     <definedName name="description_310" localSheetId="2">#REF!</definedName>
-    <definedName name="description_310" localSheetId="1">[6]Abstract!$B$60</definedName>
+    <definedName name="description_310" localSheetId="1">[4]Abstract!$B$60</definedName>
     <definedName name="description_310">#REF!</definedName>
     <definedName name="description_312" localSheetId="0">#REF!</definedName>
     <definedName name="description_312" localSheetId="3">#REF!</definedName>
+    <definedName name="description_312" localSheetId="4">#REF!</definedName>
     <definedName name="description_312" localSheetId="2">#REF!</definedName>
-    <definedName name="description_312" localSheetId="1">[7]Abstract!$B$61</definedName>
+    <definedName name="description_312" localSheetId="1">[5]Abstract!$B$61</definedName>
     <definedName name="description_312">#REF!</definedName>
     <definedName name="description_5">[1]Abstract!$B$171</definedName>
     <definedName name="description_6" localSheetId="0">#REF!</definedName>
     <definedName name="description_6" localSheetId="3">#REF!</definedName>
+    <definedName name="description_6" localSheetId="4">#REF!</definedName>
     <definedName name="description_6" localSheetId="2">#REF!</definedName>
-    <definedName name="description_6" localSheetId="1">[6]Abstract!$B$172</definedName>
+    <definedName name="description_6" localSheetId="1">[4]Abstract!$B$172</definedName>
     <definedName name="description_6">#REF!</definedName>
     <definedName name="description_759">[1]Abstract!$B$278</definedName>
     <definedName name="description_781" localSheetId="0">#REF!</definedName>
     <definedName name="description_781" localSheetId="3">#REF!</definedName>
+    <definedName name="description_781" localSheetId="4">#REF!</definedName>
     <definedName name="description_781" localSheetId="2">#REF!</definedName>
-    <definedName name="description_781" localSheetId="1">[8]Abstract!$B$299</definedName>
+    <definedName name="description_781" localSheetId="1">[6]Abstract!$B$299</definedName>
     <definedName name="description_781">#REF!</definedName>
     <definedName name="description_783">[1]Abstract!$B$301</definedName>
     <definedName name="description_784">[3]Abstract!$B$300</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">estimate!$A$1:$K$42</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'original estimate'!$A$1:$K$41</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">M!$A$1:$K$48</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'original estimate'!$A$1:$K$41</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">V!$A$1:$K$48</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">WCR!$A$1:$K$27</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">estimate!$1:$8</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="3">'original estimate'!$1:$8</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">M!$1:$8</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'original estimate'!$1:$8</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">V!$1:$8</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">WCR!$1:$12</definedName>
   </definedNames>
@@ -87,7 +94,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="72">
   <si>
     <t>Government of Nepal</t>
   </si>
@@ -307,24 +314,9 @@
     <t xml:space="preserve">Work Finished:           </t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Project:- </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Preeti"/>
-      </rPr>
-      <t>v'bf] ksfpg] el6 r'nf]</t>
-    </r>
-  </si>
-  <si>
     <t xml:space="preserve">F.Y:2082/2083            </t>
   </si>
   <si>
-    <t xml:space="preserve">Date:2082/11/10       </t>
-  </si>
-  <si>
     <t>S.No.</t>
   </si>
   <si>
@@ -344,6 +336,15 @@
   </si>
   <si>
     <t xml:space="preserve">Quantity </t>
+  </si>
+  <si>
+    <t>Detail Quantity Measurement Sheet</t>
+  </si>
+  <si>
+    <t>Date:2082/12/09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Date:2082/12/09       </t>
   </si>
 </sst>
 </file>
@@ -589,7 +590,7 @@
     <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="86">
+  <cellXfs count="90">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -699,88 +700,18 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="17" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -816,6 +747,84 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1059,77 +1068,6 @@
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
-      <sheetName val="estimate"/>
-      <sheetName val="valuation"/>
-      <sheetName val="WCR"/>
-      <sheetName val="m"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="6">
-          <cell r="A6" t="str">
-            <v>Project:-तिनघरे बाटो स्तरोन्नति</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="A7" t="str">
-            <v>Location:- Shankharapur Municipality 1</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1">
-        <row r="12">
-          <cell r="G12">
-            <v>63.93</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="estimate"/>
-      <sheetName val="V"/>
-      <sheetName val="WCR"/>
-      <sheetName val="M"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="9">
-          <cell r="A9">
-            <v>1</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1">
-        <row r="27">
-          <cell r="G27">
-            <v>495.88546019506242</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink6.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
       <sheetName val="Datasheet"/>
       <sheetName val="Abstract"/>
       <sheetName val="Quantity_Sheet"/>
@@ -1190,7 +1128,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -1249,7 +1187,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink6.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -1303,6 +1241,42 @@
       <sheetData sheetId="18" refreshError="1"/>
       <sheetData sheetId="19" refreshError="1"/>
       <sheetData sheetId="20" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink7.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="estimate"/>
+      <sheetName val="valuation"/>
+      <sheetName val="WCR"/>
+      <sheetName val="m"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="6">
+          <cell r="A6" t="str">
+            <v>Project:-तिनघरे बाटो स्तरोन्नति</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="A7" t="str">
+            <v>Location:- Shankharapur Municipality 1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1">
+        <row r="12">
+          <cell r="G12">
+            <v>63.93</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1614,113 +1588,113 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A1" s="52" t="s">
+      <c r="A1" s="77" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-      <c r="F1" s="52"/>
-      <c r="G1" s="52"/>
-      <c r="H1" s="52"/>
-      <c r="I1" s="52"/>
-      <c r="J1" s="52"/>
-      <c r="K1" s="52"/>
+      <c r="B1" s="77"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="77"/>
+      <c r="G1" s="77"/>
+      <c r="H1" s="77"/>
+      <c r="I1" s="77"/>
+      <c r="J1" s="77"/>
+      <c r="K1" s="77"/>
     </row>
     <row r="2" spans="1:19" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="53" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="53"/>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
-      <c r="I2" s="53"/>
-      <c r="J2" s="53"/>
-      <c r="K2" s="53"/>
+      <c r="A2" s="78" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
+      <c r="K2" s="78"/>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A3" s="54" t="s">
+      <c r="A3" s="79" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="54"/>
-      <c r="C3" s="54"/>
-      <c r="D3" s="54"/>
-      <c r="E3" s="54"/>
-      <c r="F3" s="54"/>
-      <c r="G3" s="54"/>
-      <c r="H3" s="54"/>
-      <c r="I3" s="54"/>
-      <c r="J3" s="54"/>
-      <c r="K3" s="54"/>
+      <c r="B3" s="79"/>
+      <c r="C3" s="79"/>
+      <c r="D3" s="79"/>
+      <c r="E3" s="79"/>
+      <c r="F3" s="79"/>
+      <c r="G3" s="79"/>
+      <c r="H3" s="79"/>
+      <c r="I3" s="79"/>
+      <c r="J3" s="79"/>
+      <c r="K3" s="79"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A4" s="54" t="s">
+      <c r="A4" s="79" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="54"/>
-      <c r="C4" s="54"/>
-      <c r="D4" s="54"/>
-      <c r="E4" s="54"/>
-      <c r="F4" s="54"/>
-      <c r="G4" s="54"/>
-      <c r="H4" s="54"/>
-      <c r="I4" s="54"/>
-      <c r="J4" s="54"/>
-      <c r="K4" s="54"/>
+      <c r="B4" s="79"/>
+      <c r="C4" s="79"/>
+      <c r="D4" s="79"/>
+      <c r="E4" s="79"/>
+      <c r="F4" s="79"/>
+      <c r="G4" s="79"/>
+      <c r="H4" s="79"/>
+      <c r="I4" s="79"/>
+      <c r="J4" s="79"/>
+      <c r="K4" s="79"/>
     </row>
     <row r="5" spans="1:19" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A5" s="55" t="s">
+      <c r="A5" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="55"/>
-      <c r="C5" s="55"/>
-      <c r="D5" s="55"/>
-      <c r="E5" s="55"/>
-      <c r="F5" s="55"/>
-      <c r="G5" s="55"/>
-      <c r="H5" s="55"/>
-      <c r="I5" s="55"/>
-      <c r="J5" s="55"/>
-      <c r="K5" s="55"/>
+      <c r="B5" s="80"/>
+      <c r="C5" s="80"/>
+      <c r="D5" s="80"/>
+      <c r="E5" s="80"/>
+      <c r="F5" s="80"/>
+      <c r="G5" s="80"/>
+      <c r="H5" s="80"/>
+      <c r="I5" s="80"/>
+      <c r="J5" s="80"/>
+      <c r="K5" s="80"/>
     </row>
     <row r="6" spans="1:19" ht="18" x14ac:dyDescent="0.25">
-      <c r="A6" s="50" t="s">
+      <c r="A6" s="67" t="s">
         <v>46</v>
       </c>
-      <c r="B6" s="50"/>
-      <c r="C6" s="50"/>
-      <c r="D6" s="50"/>
-      <c r="E6" s="50"/>
-      <c r="F6" s="50"/>
+      <c r="B6" s="67"/>
+      <c r="C6" s="67"/>
+      <c r="D6" s="67"/>
+      <c r="E6" s="67"/>
+      <c r="F6" s="67"/>
       <c r="G6" s="10"/>
-      <c r="H6" s="51" t="s">
+      <c r="H6" s="76" t="s">
         <v>25</v>
       </c>
-      <c r="I6" s="51"/>
-      <c r="J6" s="51"/>
-      <c r="K6" s="51"/>
+      <c r="I6" s="76"/>
+      <c r="J6" s="76"/>
+      <c r="K6" s="76"/>
     </row>
     <row r="7" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="45" t="s">
+      <c r="A7" s="83" t="s">
         <v>35</v>
       </c>
-      <c r="B7" s="45"/>
-      <c r="C7" s="45"/>
-      <c r="D7" s="45"/>
-      <c r="E7" s="45"/>
-      <c r="F7" s="45"/>
+      <c r="B7" s="83"/>
+      <c r="C7" s="83"/>
+      <c r="D7" s="83"/>
+      <c r="E7" s="83"/>
+      <c r="F7" s="83"/>
       <c r="G7" s="11"/>
-      <c r="H7" s="46" t="s">
+      <c r="H7" s="84" t="s">
         <v>34</v>
       </c>
-      <c r="I7" s="46"/>
-      <c r="J7" s="46"/>
-      <c r="K7" s="46"/>
+      <c r="I7" s="84"/>
+      <c r="J7" s="84"/>
+      <c r="K7" s="84"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
@@ -2363,11 +2337,11 @@
       <c r="B37" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="C37" s="43">
+      <c r="C37" s="81">
         <f>J35</f>
         <v>336113.86499999999</v>
       </c>
-      <c r="D37" s="44"/>
+      <c r="D37" s="82"/>
       <c r="E37" s="9">
         <v>100</v>
       </c>
@@ -2389,21 +2363,21 @@
       <c r="B38" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="C38" s="47">
+      <c r="C38" s="85">
         <v>300000</v>
       </c>
-      <c r="D38" s="48"/>
+      <c r="D38" s="86"/>
       <c r="E38" s="9"/>
     </row>
     <row r="39" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B39" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="C39" s="47">
+      <c r="C39" s="85">
         <f>C38-C41-C42</f>
         <v>285000</v>
       </c>
-      <c r="D39" s="48"/>
+      <c r="D39" s="86"/>
       <c r="E39" s="9">
         <f>C39/C37*100</f>
         <v>84.79269369027665</v>
@@ -2413,11 +2387,11 @@
       <c r="B40" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="C40" s="49">
+      <c r="C40" s="87">
         <f>C37-C39</f>
         <v>51113.864999999991</v>
       </c>
-      <c r="D40" s="49"/>
+      <c r="D40" s="87"/>
       <c r="E40" s="9">
         <f>100-E39</f>
         <v>15.20730630972335</v>
@@ -2427,11 +2401,11 @@
       <c r="B41" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="C41" s="43">
+      <c r="C41" s="81">
         <f>C38*0.03</f>
         <v>9000</v>
       </c>
-      <c r="D41" s="44"/>
+      <c r="D41" s="82"/>
       <c r="E41" s="9">
         <v>3</v>
       </c>
@@ -2440,24 +2414,17 @@
       <c r="B42" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="C42" s="43">
+      <c r="C42" s="81">
         <f>C38*0.02</f>
         <v>6000</v>
       </c>
-      <c r="D42" s="44"/>
+      <c r="D42" s="82"/>
       <c r="E42" s="9">
         <v>2</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="H6:K6"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A4:K4"/>
-    <mergeCell ref="A5:K5"/>
     <mergeCell ref="C41:D41"/>
     <mergeCell ref="C42:D42"/>
     <mergeCell ref="A7:F7"/>
@@ -2466,6 +2433,13 @@
     <mergeCell ref="C38:D38"/>
     <mergeCell ref="C39:D39"/>
     <mergeCell ref="C40:D40"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="H6:K6"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A4:K4"/>
+    <mergeCell ref="A5:K5"/>
   </mergeCells>
   <pageMargins left="0.70866141732283505" right="0.70866141732283505" top="0.74803149606299202" bottom="0.74803149606299202" header="0.31496062992126" footer="0.31496062992126"/>
   <pageSetup paperSize="9" scale="80" orientation="portrait" verticalDpi="1200" r:id="rId1"/>
@@ -2495,110 +2469,110 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="56" t="s">
+      <c r="A1" s="70" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
-      <c r="I1" s="56"/>
-      <c r="J1" s="56"/>
-      <c r="K1" s="56"/>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
+      <c r="H1" s="70"/>
+      <c r="I1" s="70"/>
+      <c r="J1" s="70"/>
+      <c r="K1" s="70"/>
     </row>
     <row r="2" spans="1:13" ht="25.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="57"/>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57"/>
-      <c r="I2" s="57"/>
-      <c r="J2" s="57"/>
-      <c r="K2" s="57"/>
+      <c r="A2" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="71"/>
+      <c r="C2" s="71"/>
+      <c r="D2" s="71"/>
+      <c r="E2" s="71"/>
+      <c r="F2" s="71"/>
+      <c r="G2" s="71"/>
+      <c r="H2" s="71"/>
+      <c r="I2" s="71"/>
+      <c r="J2" s="71"/>
+      <c r="K2" s="71"/>
     </row>
     <row r="3" spans="1:13" s="35" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="58" t="s">
+      <c r="A3" s="72" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="58"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="58"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="58"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="58"/>
-      <c r="I3" s="58"/>
-      <c r="J3" s="58"/>
-      <c r="K3" s="58"/>
+      <c r="B3" s="72"/>
+      <c r="C3" s="72"/>
+      <c r="D3" s="72"/>
+      <c r="E3" s="72"/>
+      <c r="F3" s="72"/>
+      <c r="G3" s="72"/>
+      <c r="H3" s="72"/>
+      <c r="I3" s="72"/>
+      <c r="J3" s="72"/>
+      <c r="K3" s="72"/>
     </row>
     <row r="4" spans="1:13" s="35" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="58" t="s">
+      <c r="A4" s="72" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="58"/>
-      <c r="C4" s="58"/>
-      <c r="D4" s="58"/>
-      <c r="E4" s="58"/>
-      <c r="F4" s="58"/>
-      <c r="G4" s="58"/>
-      <c r="H4" s="58"/>
-      <c r="I4" s="58"/>
-      <c r="J4" s="58"/>
-      <c r="K4" s="58"/>
+      <c r="B4" s="72"/>
+      <c r="C4" s="72"/>
+      <c r="D4" s="72"/>
+      <c r="E4" s="72"/>
+      <c r="F4" s="72"/>
+      <c r="G4" s="72"/>
+      <c r="H4" s="72"/>
+      <c r="I4" s="72"/>
+      <c r="J4" s="72"/>
+      <c r="K4" s="72"/>
     </row>
     <row r="5" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A5" s="59" t="s">
+      <c r="A5" s="73" t="s">
         <v>56</v>
       </c>
-      <c r="B5" s="59"/>
-      <c r="C5" s="59"/>
-      <c r="D5" s="59"/>
-      <c r="E5" s="59"/>
-      <c r="F5" s="59"/>
-      <c r="G5" s="59"/>
-      <c r="H5" s="59"/>
-      <c r="I5" s="59"/>
-      <c r="J5" s="59"/>
-      <c r="K5" s="59"/>
+      <c r="B5" s="73"/>
+      <c r="C5" s="73"/>
+      <c r="D5" s="73"/>
+      <c r="E5" s="73"/>
+      <c r="F5" s="73"/>
+      <c r="G5" s="73"/>
+      <c r="H5" s="73"/>
+      <c r="I5" s="73"/>
+      <c r="J5" s="73"/>
+      <c r="K5" s="73"/>
     </row>
     <row r="6" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A6" s="60" t="s">
+      <c r="A6" s="45" t="s">
         <v>57</v>
       </c>
-      <c r="B6" s="60"/>
-      <c r="C6" s="61">
+      <c r="B6" s="45"/>
+      <c r="C6" s="74">
         <f>F27</f>
         <v>336113.86499999999</v>
       </c>
-      <c r="D6" s="62"/>
-      <c r="E6" s="63"/>
-      <c r="F6" s="60"/>
-      <c r="G6" s="60"/>
-      <c r="H6" s="60" t="s">
+      <c r="D6" s="75"/>
+      <c r="E6" s="46"/>
+      <c r="F6" s="45"/>
+      <c r="G6" s="45"/>
+      <c r="H6" s="45" t="s">
         <v>58</v>
       </c>
-      <c r="I6" s="60"/>
-      <c r="J6" s="61">
+      <c r="I6" s="45"/>
+      <c r="J6" s="74">
         <f>I27</f>
-        <v>219957.57467999999</v>
-      </c>
-      <c r="K6" s="62"/>
+        <v>208459.4124</v>
+      </c>
+      <c r="K6" s="75"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A7" s="64" t="s">
+      <c r="A7" s="47" t="s">
         <v>59</v>
       </c>
-      <c r="B7" s="64"/>
-      <c r="C7" s="64"/>
-      <c r="D7" s="64"/>
+      <c r="B7" s="47"/>
+      <c r="C7" s="47"/>
+      <c r="D7" s="47"/>
       <c r="F7" s="65"/>
       <c r="G7" s="65"/>
       <c r="I7" s="66" t="s">
@@ -2607,528 +2581,541 @@
       <c r="J7" s="66"/>
       <c r="K7" s="66"/>
     </row>
-    <row r="8" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="50" t="s">
+    <row r="8" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A8" s="67" t="s">
+        <v>46</v>
+      </c>
+      <c r="B8" s="67"/>
+      <c r="C8" s="67"/>
+      <c r="D8" s="67"/>
+      <c r="E8" s="67"/>
+      <c r="F8" s="67"/>
+      <c r="I8" s="68" t="s">
         <v>61</v>
       </c>
-      <c r="B8" s="50"/>
-      <c r="C8" s="50"/>
-      <c r="D8" s="50"/>
-      <c r="E8" s="50"/>
-      <c r="F8" s="50"/>
-      <c r="I8" s="67" t="s">
+      <c r="J8" s="68"/>
+      <c r="K8" s="68"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A9" s="69" t="str">
+        <f>[7]estimate!A7</f>
+        <v>Location:- Shankharapur Municipality 1</v>
+      </c>
+      <c r="B9" s="69"/>
+      <c r="C9" s="69"/>
+      <c r="D9" s="69"/>
+      <c r="E9" s="69"/>
+      <c r="F9" s="69"/>
+      <c r="I9" s="68" t="s">
+        <v>71</v>
+      </c>
+      <c r="J9" s="68"/>
+      <c r="K9" s="68"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A11" s="63" t="s">
         <v>62</v>
       </c>
-      <c r="J8" s="67"/>
-      <c r="K8" s="67"/>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A9" s="68" t="str">
-        <f>[4]estimate!A7</f>
-        <v>Location:- Shankharapur Municipality 1</v>
-      </c>
-      <c r="B9" s="68"/>
-      <c r="C9" s="68"/>
-      <c r="D9" s="68"/>
-      <c r="E9" s="68"/>
-      <c r="F9" s="68"/>
-      <c r="I9" s="67" t="s">
+      <c r="B11" s="63" t="s">
         <v>63</v>
       </c>
-      <c r="J9" s="67"/>
-      <c r="K9" s="67"/>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A11" s="69" t="s">
+      <c r="C11" s="63" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" s="64" t="s">
         <v>64</v>
       </c>
-      <c r="B11" s="69" t="s">
+      <c r="E11" s="64"/>
+      <c r="F11" s="64"/>
+      <c r="G11" s="64" t="s">
         <v>65</v>
       </c>
-      <c r="C11" s="69" t="s">
-        <v>12</v>
-      </c>
-      <c r="D11" s="70" t="s">
+      <c r="H11" s="64"/>
+      <c r="I11" s="64"/>
+      <c r="J11" s="63" t="s">
         <v>66</v>
       </c>
-      <c r="E11" s="70"/>
-      <c r="F11" s="70"/>
-      <c r="G11" s="70" t="s">
+      <c r="K11" s="62" t="s">
         <v>67</v>
       </c>
-      <c r="H11" s="70"/>
-      <c r="I11" s="70"/>
-      <c r="J11" s="69" t="s">
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A12" s="63"/>
+      <c r="B12" s="63"/>
+      <c r="C12" s="63"/>
+      <c r="D12" s="48" t="s">
         <v>68</v>
       </c>
-      <c r="K11" s="71" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A12" s="69"/>
-      <c r="B12" s="69"/>
-      <c r="C12" s="69"/>
-      <c r="D12" s="72" t="s">
-        <v>70</v>
-      </c>
-      <c r="E12" s="72" t="s">
+      <c r="E12" s="48" t="s">
         <v>13</v>
       </c>
-      <c r="F12" s="72" t="s">
+      <c r="F12" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="G12" s="72" t="s">
-        <v>70</v>
-      </c>
-      <c r="H12" s="72" t="s">
+      <c r="G12" s="48" t="s">
+        <v>68</v>
+      </c>
+      <c r="H12" s="48" t="s">
         <v>13</v>
       </c>
-      <c r="I12" s="72" t="s">
+      <c r="I12" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="J12" s="69"/>
-      <c r="K12" s="71"/>
+      <c r="J12" s="63"/>
+      <c r="K12" s="62"/>
     </row>
     <row r="13" spans="1:13" s="35" customFormat="1" ht="33" x14ac:dyDescent="0.25">
-      <c r="A13" s="73">
+      <c r="A13" s="49">
         <f>estimate!A9</f>
         <v>1</v>
       </c>
       <c r="B13" s="39" t="s">
         <v>47</v>
       </c>
-      <c r="C13" s="74" t="str">
+      <c r="C13" s="50" t="str">
         <f>estimate!H13</f>
         <v>cum</v>
       </c>
-      <c r="D13" s="74">
+      <c r="D13" s="50">
         <f>estimate!G13</f>
         <v>99.9</v>
       </c>
-      <c r="E13" s="74">
+      <c r="E13" s="50">
         <f>estimate!I13</f>
         <v>963.05</v>
       </c>
-      <c r="F13" s="74">
+      <c r="F13" s="50">
         <f>D13*E13</f>
         <v>96208.695000000007</v>
       </c>
-      <c r="G13" s="74">
+      <c r="G13" s="50">
         <f>V!G16</f>
-        <v>97.289999999999992</v>
-      </c>
-      <c r="H13" s="74">
+        <v>88.199999999999989</v>
+      </c>
+      <c r="H13" s="50">
         <f>V!I16</f>
         <v>963.05</v>
       </c>
-      <c r="I13" s="74">
+      <c r="I13" s="50">
         <f>G13*H13</f>
-        <v>93695.134499999986</v>
-      </c>
-      <c r="J13" s="75">
+        <v>84941.00999999998</v>
+      </c>
+      <c r="J13" s="51">
         <f>I13-F13</f>
-        <v>-2513.5605000000214</v>
-      </c>
-      <c r="K13" s="76"/>
+        <v>-11267.685000000027</v>
+      </c>
+      <c r="K13" s="52"/>
       <c r="M13" s="35">
         <f>1.25*F13</f>
         <v>120260.86875000001</v>
       </c>
     </row>
     <row r="14" spans="1:13" s="35" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="78"/>
-      <c r="B14" s="79"/>
-      <c r="C14" s="74"/>
-      <c r="D14" s="74"/>
-      <c r="E14" s="74"/>
-      <c r="F14" s="74"/>
-      <c r="G14" s="74"/>
-      <c r="H14" s="74"/>
-      <c r="I14" s="74"/>
-      <c r="J14" s="75"/>
-      <c r="K14" s="76"/>
+      <c r="A14" s="54"/>
+      <c r="B14" s="55"/>
+      <c r="C14" s="50"/>
+      <c r="D14" s="50"/>
+      <c r="E14" s="50"/>
+      <c r="F14" s="50"/>
+      <c r="G14" s="50"/>
+      <c r="H14" s="50"/>
+      <c r="I14" s="50"/>
+      <c r="J14" s="51"/>
+      <c r="K14" s="52"/>
     </row>
     <row r="15" spans="1:13" s="35" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A15" s="73">
+      <c r="A15" s="49">
         <f>estimate!A15</f>
         <v>2</v>
       </c>
-      <c r="B15" s="85" t="str">
+      <c r="B15" s="61" t="str">
         <f>estimate!B15</f>
         <v>Laying and joining of 32 mmØ HDPE pipe with butt-weld joints</v>
       </c>
-      <c r="C15" s="74" t="str">
+      <c r="C15" s="50" t="str">
         <f>estimate!H17</f>
         <v>rm</v>
       </c>
-      <c r="D15" s="74">
+      <c r="D15" s="50">
         <f>estimate!G17</f>
         <v>1900</v>
       </c>
-      <c r="E15" s="74">
+      <c r="E15" s="50">
         <f>estimate!I17</f>
         <v>5.3194999999999997</v>
       </c>
-      <c r="F15" s="74">
+      <c r="F15" s="50">
         <f>D15*E15</f>
         <v>10107.049999999999</v>
       </c>
-      <c r="G15" s="74">
+      <c r="G15" s="50">
         <f>V!G20</f>
-        <v>1078</v>
-      </c>
-      <c r="H15" s="74">
+        <v>0</v>
+      </c>
+      <c r="H15" s="50">
         <f>V!I20</f>
         <v>5.3194999999999997</v>
       </c>
-      <c r="I15" s="74">
+      <c r="I15" s="50">
         <f>G15*H15</f>
-        <v>5734.4209999999994</v>
-      </c>
-      <c r="J15" s="75">
+        <v>0</v>
+      </c>
+      <c r="J15" s="51">
         <f>I15-F15</f>
-        <v>-4372.6289999999999</v>
-      </c>
-      <c r="K15" s="76"/>
+        <v>-10107.049999999999</v>
+      </c>
+      <c r="K15" s="52"/>
       <c r="M15" s="35">
         <f t="shared" ref="M15:M23" si="0">1.25*F15</f>
         <v>12633.8125</v>
       </c>
     </row>
     <row r="16" spans="1:13" s="35" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A16" s="73"/>
-      <c r="B16" s="85"/>
-      <c r="C16" s="74"/>
-      <c r="D16" s="74"/>
-      <c r="E16" s="74"/>
-      <c r="F16" s="74"/>
-      <c r="G16" s="74"/>
-      <c r="H16" s="74"/>
-      <c r="I16" s="74"/>
-      <c r="J16" s="75"/>
-      <c r="K16" s="76"/>
+      <c r="A16" s="49"/>
+      <c r="B16" s="61"/>
+      <c r="C16" s="50"/>
+      <c r="D16" s="50"/>
+      <c r="E16" s="50"/>
+      <c r="F16" s="50"/>
+      <c r="G16" s="50"/>
+      <c r="H16" s="50"/>
+      <c r="I16" s="50"/>
+      <c r="J16" s="51"/>
+      <c r="K16" s="52"/>
     </row>
     <row r="17" spans="1:13" s="35" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A17" s="73">
+      <c r="A17" s="49">
         <f>estimate!A19</f>
         <v>3</v>
       </c>
-      <c r="B17" s="85" t="str">
+      <c r="B17" s="61" t="str">
         <f>estimate!B19</f>
         <v>-High Density Polythene Pipe NS 40 pipe material PE 100, PN 16</v>
       </c>
-      <c r="C17" s="74" t="str">
+      <c r="C17" s="50" t="str">
         <f>estimate!H23</f>
         <v>kg</v>
       </c>
-      <c r="D17" s="74">
+      <c r="D17" s="50">
         <f>estimate!G23</f>
         <v>676</v>
       </c>
-      <c r="E17" s="74">
+      <c r="E17" s="50">
         <f>estimate!I23</f>
         <v>287</v>
       </c>
-      <c r="F17" s="74">
+      <c r="F17" s="50">
         <f>D17*E17</f>
         <v>194012</v>
       </c>
-      <c r="G17" s="74">
+      <c r="G17" s="50">
         <f>V!G29</f>
-        <v>365.37800000000004</v>
-      </c>
-      <c r="H17" s="74">
+        <v>365.03999999999996</v>
+      </c>
+      <c r="H17" s="50">
         <f>V!I29</f>
         <v>287</v>
       </c>
-      <c r="I17" s="74">
+      <c r="I17" s="50">
         <f>G17*H17</f>
-        <v>104863.48600000002</v>
-      </c>
-      <c r="J17" s="75">
+        <v>104766.48</v>
+      </c>
+      <c r="J17" s="51">
         <f>I17-F17</f>
-        <v>-89148.513999999981</v>
-      </c>
-      <c r="K17" s="76"/>
+        <v>-89245.52</v>
+      </c>
+      <c r="K17" s="52"/>
       <c r="M17" s="35">
         <f t="shared" si="0"/>
         <v>242515</v>
       </c>
     </row>
     <row r="18" spans="1:13" s="35" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A18" s="73"/>
-      <c r="B18" s="77" t="str">
+      <c r="A18" s="49"/>
+      <c r="B18" s="53" t="str">
         <f>estimate!B24</f>
         <v>-13% VAT for material</v>
       </c>
-      <c r="C18" s="74"/>
-      <c r="D18" s="74"/>
-      <c r="E18" s="74"/>
-      <c r="F18" s="74">
+      <c r="C18" s="50"/>
+      <c r="D18" s="50"/>
+      <c r="E18" s="50"/>
+      <c r="F18" s="50">
         <f>estimate!J24</f>
         <v>25221.56</v>
       </c>
-      <c r="G18" s="74"/>
-      <c r="H18" s="74"/>
-      <c r="I18" s="74">
+      <c r="G18" s="50"/>
+      <c r="H18" s="50"/>
+      <c r="I18" s="50">
         <f>V!J30</f>
-        <v>13632.253180000003</v>
-      </c>
-      <c r="J18" s="75">
+        <v>13619.642400000001</v>
+      </c>
+      <c r="J18" s="51">
         <f>I18-F18</f>
-        <v>-11589.306819999998</v>
-      </c>
-      <c r="K18" s="76"/>
+        <v>-11601.917600000001</v>
+      </c>
+      <c r="K18" s="52"/>
       <c r="M18" s="35">
         <f t="shared" ref="M18" si="1">1.25*F18</f>
         <v>31526.95</v>
       </c>
     </row>
     <row r="19" spans="1:13" s="35" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="78"/>
-      <c r="B19" s="79"/>
-      <c r="C19" s="74"/>
-      <c r="D19" s="74"/>
-      <c r="E19" s="74"/>
-      <c r="F19" s="74"/>
-      <c r="G19" s="74"/>
-      <c r="H19" s="74"/>
-      <c r="I19" s="74"/>
-      <c r="J19" s="75"/>
-      <c r="K19" s="76"/>
+      <c r="A19" s="54"/>
+      <c r="B19" s="55"/>
+      <c r="C19" s="50"/>
+      <c r="D19" s="50"/>
+      <c r="E19" s="50"/>
+      <c r="F19" s="50"/>
+      <c r="G19" s="50"/>
+      <c r="H19" s="50"/>
+      <c r="I19" s="50"/>
+      <c r="J19" s="51"/>
+      <c r="K19" s="52"/>
     </row>
     <row r="20" spans="1:13" s="35" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A20" s="73">
+      <c r="A20" s="49">
         <f>estimate!A26</f>
         <v>4</v>
       </c>
-      <c r="B20" s="85" t="str">
+      <c r="B20" s="61" t="str">
         <f>estimate!B26</f>
         <v>32mm GI pipe threaded</v>
       </c>
-      <c r="C20" s="74" t="str">
+      <c r="C20" s="50" t="str">
         <f>estimate!H28</f>
         <v>rm</v>
       </c>
-      <c r="D20" s="74">
+      <c r="D20" s="50">
         <f>estimate!G28</f>
         <v>6</v>
       </c>
-      <c r="E20" s="74">
+      <c r="E20" s="50">
         <f>estimate!I28</f>
         <v>452</v>
       </c>
-      <c r="F20" s="74">
+      <c r="F20" s="50">
         <f>D20*E20</f>
         <v>2712</v>
       </c>
-      <c r="G20" s="74">
+      <c r="G20" s="50">
         <f>V!G34</f>
         <v>3</v>
       </c>
-      <c r="H20" s="74">
+      <c r="H20" s="50">
         <f>V!I34</f>
         <v>452</v>
       </c>
-      <c r="I20" s="74">
+      <c r="I20" s="50">
         <f>G20*H20</f>
         <v>1356</v>
       </c>
-      <c r="J20" s="75">
+      <c r="J20" s="51">
         <f>I20-F20</f>
         <v>-1356</v>
       </c>
-      <c r="K20" s="76"/>
+      <c r="K20" s="52"/>
       <c r="M20" s="35">
         <f t="shared" si="0"/>
         <v>3390</v>
       </c>
     </row>
     <row r="21" spans="1:13" s="35" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A21" s="73"/>
-      <c r="B21" s="77" t="str">
+      <c r="A21" s="49"/>
+      <c r="B21" s="53" t="str">
         <f>estimate!B29</f>
         <v>-13% VAT for material</v>
       </c>
-      <c r="C21" s="74"/>
-      <c r="D21" s="74"/>
-      <c r="E21" s="74"/>
-      <c r="F21" s="74">
+      <c r="C21" s="50"/>
+      <c r="D21" s="50"/>
+      <c r="E21" s="50"/>
+      <c r="F21" s="50">
         <f>estimate!J29</f>
         <v>352.56</v>
       </c>
-      <c r="G21" s="74"/>
-      <c r="H21" s="74"/>
-      <c r="I21" s="74">
+      <c r="G21" s="50"/>
+      <c r="H21" s="50"/>
+      <c r="I21" s="50">
         <f>V!J35</f>
         <v>176.28</v>
       </c>
-      <c r="J21" s="75">
+      <c r="J21" s="51">
         <f>I21-F21</f>
         <v>-176.28</v>
       </c>
-      <c r="K21" s="76"/>
+      <c r="K21" s="52"/>
       <c r="M21" s="35">
         <f t="shared" si="0"/>
         <v>440.7</v>
       </c>
     </row>
     <row r="22" spans="1:13" s="35" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="78"/>
-      <c r="B22" s="79"/>
-      <c r="C22" s="74"/>
-      <c r="D22" s="74"/>
-      <c r="E22" s="74"/>
-      <c r="F22" s="74"/>
-      <c r="G22" s="74"/>
-      <c r="H22" s="74"/>
-      <c r="I22" s="74"/>
-      <c r="J22" s="75"/>
-      <c r="K22" s="76"/>
+      <c r="A22" s="54"/>
+      <c r="B22" s="55"/>
+      <c r="C22" s="50"/>
+      <c r="D22" s="50"/>
+      <c r="E22" s="50"/>
+      <c r="F22" s="50"/>
+      <c r="G22" s="50"/>
+      <c r="H22" s="50"/>
+      <c r="I22" s="50"/>
+      <c r="J22" s="51"/>
+      <c r="K22" s="52"/>
     </row>
     <row r="23" spans="1:13" s="35" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A23" s="73">
+      <c r="A23" s="49">
         <f>estimate!A31</f>
         <v>5</v>
       </c>
-      <c r="B23" s="85" t="str">
+      <c r="B23" s="61" t="str">
         <f>estimate!B31</f>
         <v>Provisional sum for other unforseen works</v>
       </c>
-      <c r="C23" s="74" t="str">
+      <c r="C23" s="50" t="str">
         <f>estimate!H31</f>
         <v>PS</v>
       </c>
-      <c r="D23" s="74">
+      <c r="D23" s="50">
         <f>estimate!G31</f>
         <v>1</v>
       </c>
-      <c r="E23" s="74">
+      <c r="E23" s="50">
         <f>estimate!I31</f>
         <v>7000</v>
       </c>
-      <c r="F23" s="74">
+      <c r="F23" s="50">
         <f>D23*E23</f>
         <v>7000</v>
       </c>
-      <c r="G23" s="74">
+      <c r="G23" s="50">
         <f>V!G37</f>
-        <v>0</v>
-      </c>
-      <c r="H23" s="74">
+        <v>1</v>
+      </c>
+      <c r="H23" s="50">
         <f>V!I37</f>
-        <v>7000</v>
-      </c>
-      <c r="I23" s="74">
+        <v>3100</v>
+      </c>
+      <c r="I23" s="50">
         <f>G23*H23</f>
-        <v>0</v>
-      </c>
-      <c r="J23" s="75">
+        <v>3100</v>
+      </c>
+      <c r="J23" s="51">
         <f>I23-F23</f>
-        <v>-7000</v>
-      </c>
-      <c r="K23" s="76"/>
+        <v>-3900</v>
+      </c>
+      <c r="K23" s="52"/>
       <c r="M23" s="35">
         <f t="shared" si="0"/>
         <v>8750</v>
       </c>
     </row>
     <row r="24" spans="1:13" s="35" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="78"/>
-      <c r="B24" s="79"/>
-      <c r="C24" s="74"/>
-      <c r="D24" s="74"/>
-      <c r="E24" s="74"/>
-      <c r="F24" s="74"/>
-      <c r="G24" s="74"/>
-      <c r="H24" s="74"/>
-      <c r="I24" s="74"/>
-      <c r="J24" s="75"/>
-      <c r="K24" s="76"/>
+      <c r="A24" s="54"/>
+      <c r="B24" s="55"/>
+      <c r="C24" s="50"/>
+      <c r="D24" s="50"/>
+      <c r="E24" s="50"/>
+      <c r="F24" s="50"/>
+      <c r="G24" s="50"/>
+      <c r="H24" s="50"/>
+      <c r="I24" s="50"/>
+      <c r="J24" s="51"/>
+      <c r="K24" s="52"/>
     </row>
     <row r="25" spans="1:13" s="35" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="73">
+      <c r="A25" s="49">
         <f>estimate!A33</f>
         <v>6</v>
       </c>
-      <c r="B25" s="80" t="str">
+      <c r="B25" s="56" t="str">
         <f>estimate!B33</f>
         <v>Information board (सुचना पाटि)</v>
       </c>
-      <c r="C25" s="74" t="str">
+      <c r="C25" s="50" t="str">
         <f>estimate!H33</f>
         <v>no.</v>
       </c>
-      <c r="D25" s="74">
+      <c r="D25" s="50">
         <f>estimate!G33</f>
         <v>1</v>
       </c>
-      <c r="E25" s="74">
+      <c r="E25" s="50">
         <f>estimate!I33</f>
         <v>500</v>
       </c>
-      <c r="F25" s="74">
+      <c r="F25" s="50">
         <f>D25*E25</f>
         <v>500</v>
       </c>
-      <c r="G25" s="74">
+      <c r="G25" s="50">
         <f>V!C39</f>
         <v>1</v>
       </c>
-      <c r="H25" s="74">
+      <c r="H25" s="50">
         <f>V!I39</f>
         <v>500</v>
       </c>
-      <c r="I25" s="74">
+      <c r="I25" s="50">
         <f>G25*H25</f>
         <v>500</v>
       </c>
-      <c r="J25" s="75">
+      <c r="J25" s="51">
         <f>I25-F25</f>
         <v>0</v>
       </c>
-      <c r="K25" s="76"/>
+      <c r="K25" s="52"/>
     </row>
     <row r="26" spans="1:13" s="35" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="79"/>
-      <c r="B26" s="79"/>
-      <c r="C26" s="74"/>
-      <c r="D26" s="74"/>
-      <c r="E26" s="74"/>
-      <c r="F26" s="74"/>
-      <c r="G26" s="74"/>
-      <c r="H26" s="74"/>
-      <c r="I26" s="74"/>
-      <c r="J26" s="75"/>
-      <c r="K26" s="76"/>
+      <c r="A26" s="55"/>
+      <c r="B26" s="55"/>
+      <c r="C26" s="50"/>
+      <c r="D26" s="50"/>
+      <c r="E26" s="50"/>
+      <c r="F26" s="50"/>
+      <c r="G26" s="50"/>
+      <c r="H26" s="50"/>
+      <c r="I26" s="50"/>
+      <c r="J26" s="51"/>
+      <c r="K26" s="52"/>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A27" s="81"/>
-      <c r="B27" s="82" t="s">
+      <c r="A27" s="57"/>
+      <c r="B27" s="58" t="s">
         <v>20</v>
       </c>
-      <c r="C27" s="82"/>
-      <c r="D27" s="83"/>
-      <c r="E27" s="83"/>
-      <c r="F27" s="83">
+      <c r="C27" s="58"/>
+      <c r="D27" s="59"/>
+      <c r="E27" s="59"/>
+      <c r="F27" s="59">
         <f>SUM(F13:F25)</f>
         <v>336113.86499999999</v>
       </c>
-      <c r="G27" s="83"/>
-      <c r="H27" s="83"/>
-      <c r="I27" s="83">
+      <c r="G27" s="59"/>
+      <c r="H27" s="59"/>
+      <c r="I27" s="59">
         <f>SUM(I13:I25)</f>
-        <v>219957.57467999999</v>
-      </c>
-      <c r="J27" s="84">
+        <v>208459.4124</v>
+      </c>
+      <c r="J27" s="60">
         <f>I27-F27</f>
-        <v>-116156.29032</v>
-      </c>
-      <c r="K27" s="81"/>
+        <v>-127654.45259999999</v>
+      </c>
+      <c r="K27" s="57"/>
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A4:K4"/>
+    <mergeCell ref="A5:K5"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="I7:K7"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="I8:K8"/>
+    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="I9:K9"/>
     <mergeCell ref="K11:K12"/>
     <mergeCell ref="A11:A12"/>
     <mergeCell ref="B11:B12"/>
@@ -3136,19 +3123,6 @@
     <mergeCell ref="D11:F11"/>
     <mergeCell ref="G11:I11"/>
     <mergeCell ref="J11:J12"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="I7:K7"/>
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="I8:K8"/>
-    <mergeCell ref="A9:F9"/>
-    <mergeCell ref="I9:K9"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A4:K4"/>
-    <mergeCell ref="A5:K5"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="J6:K6"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3181,113 +3155,113 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="52" t="s">
+      <c r="A1" s="77" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-      <c r="F1" s="52"/>
-      <c r="G1" s="52"/>
-      <c r="H1" s="52"/>
-      <c r="I1" s="52"/>
-      <c r="J1" s="52"/>
-      <c r="K1" s="52"/>
+      <c r="B1" s="77"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="77"/>
+      <c r="G1" s="77"/>
+      <c r="H1" s="77"/>
+      <c r="I1" s="77"/>
+      <c r="J1" s="77"/>
+      <c r="K1" s="77"/>
     </row>
     <row r="2" spans="1:11" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="53" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="53"/>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
-      <c r="I2" s="53"/>
-      <c r="J2" s="53"/>
-      <c r="K2" s="53"/>
+      <c r="A2" s="78" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
+      <c r="K2" s="78"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="54" t="s">
+      <c r="A3" s="79" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="54"/>
-      <c r="C3" s="54"/>
-      <c r="D3" s="54"/>
-      <c r="E3" s="54"/>
-      <c r="F3" s="54"/>
-      <c r="G3" s="54"/>
-      <c r="H3" s="54"/>
-      <c r="I3" s="54"/>
-      <c r="J3" s="54"/>
-      <c r="K3" s="54"/>
+      <c r="B3" s="79"/>
+      <c r="C3" s="79"/>
+      <c r="D3" s="79"/>
+      <c r="E3" s="79"/>
+      <c r="F3" s="79"/>
+      <c r="G3" s="79"/>
+      <c r="H3" s="79"/>
+      <c r="I3" s="79"/>
+      <c r="J3" s="79"/>
+      <c r="K3" s="79"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="54" t="s">
+      <c r="A4" s="79" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="54"/>
-      <c r="C4" s="54"/>
-      <c r="D4" s="54"/>
-      <c r="E4" s="54"/>
-      <c r="F4" s="54"/>
-      <c r="G4" s="54"/>
-      <c r="H4" s="54"/>
-      <c r="I4" s="54"/>
-      <c r="J4" s="54"/>
-      <c r="K4" s="54"/>
+      <c r="B4" s="79"/>
+      <c r="C4" s="79"/>
+      <c r="D4" s="79"/>
+      <c r="E4" s="79"/>
+      <c r="F4" s="79"/>
+      <c r="G4" s="79"/>
+      <c r="H4" s="79"/>
+      <c r="I4" s="79"/>
+      <c r="J4" s="79"/>
+      <c r="K4" s="79"/>
     </row>
     <row r="5" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A5" s="55" t="s">
+      <c r="A5" s="80" t="s">
         <v>48</v>
       </c>
-      <c r="B5" s="55"/>
-      <c r="C5" s="55"/>
-      <c r="D5" s="55"/>
-      <c r="E5" s="55"/>
-      <c r="F5" s="55"/>
-      <c r="G5" s="55"/>
-      <c r="H5" s="55"/>
-      <c r="I5" s="55"/>
-      <c r="J5" s="55"/>
-      <c r="K5" s="55"/>
+      <c r="B5" s="80"/>
+      <c r="C5" s="80"/>
+      <c r="D5" s="80"/>
+      <c r="E5" s="80"/>
+      <c r="F5" s="80"/>
+      <c r="G5" s="80"/>
+      <c r="H5" s="80"/>
+      <c r="I5" s="80"/>
+      <c r="J5" s="80"/>
+      <c r="K5" s="80"/>
     </row>
     <row r="6" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A6" s="50" t="s">
+      <c r="A6" s="67" t="s">
         <v>46</v>
       </c>
-      <c r="B6" s="50"/>
-      <c r="C6" s="50"/>
-      <c r="D6" s="50"/>
-      <c r="E6" s="50"/>
-      <c r="F6" s="50"/>
+      <c r="B6" s="67"/>
+      <c r="C6" s="67"/>
+      <c r="D6" s="67"/>
+      <c r="E6" s="67"/>
+      <c r="F6" s="67"/>
       <c r="G6" s="10"/>
-      <c r="H6" s="51" t="s">
+      <c r="H6" s="76" t="s">
         <v>25</v>
       </c>
-      <c r="I6" s="51"/>
-      <c r="J6" s="51"/>
-      <c r="K6" s="51"/>
+      <c r="I6" s="76"/>
+      <c r="J6" s="76"/>
+      <c r="K6" s="76"/>
     </row>
     <row r="7" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="45" t="s">
+      <c r="A7" s="83" t="s">
         <v>35</v>
       </c>
-      <c r="B7" s="45"/>
-      <c r="C7" s="45"/>
-      <c r="D7" s="45"/>
-      <c r="E7" s="45"/>
-      <c r="F7" s="45"/>
+      <c r="B7" s="83"/>
+      <c r="C7" s="83"/>
+      <c r="D7" s="83"/>
+      <c r="E7" s="83"/>
+      <c r="F7" s="83"/>
       <c r="G7" s="11"/>
-      <c r="H7" s="46" t="s">
-        <v>34</v>
-      </c>
-      <c r="I7" s="46"/>
-      <c r="J7" s="46"/>
-      <c r="K7" s="46"/>
+      <c r="H7" s="84" t="s">
+        <v>70</v>
+      </c>
+      <c r="I7" s="84"/>
+      <c r="J7" s="84"/>
+      <c r="K7" s="84"/>
     </row>
     <row r="8" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
@@ -3350,8 +3324,8 @@
         <v>1</v>
       </c>
       <c r="D10" s="33">
-        <f>90+38+40</f>
-        <v>168</v>
+        <f>90+38+40-1</f>
+        <v>167</v>
       </c>
       <c r="E10" s="17">
         <v>0.3</v>
@@ -3361,7 +3335,7 @@
       </c>
       <c r="G10" s="33">
         <f t="shared" ref="G10:G12" si="0">PRODUCT(C10:F10)</f>
-        <v>15.12</v>
+        <v>15.03</v>
       </c>
       <c r="H10" s="17"/>
       <c r="I10" s="17"/>
@@ -3377,8 +3351,8 @@
         <v>1</v>
       </c>
       <c r="D11" s="33">
-        <f>40+43</f>
-        <v>83</v>
+        <f>40+43-2</f>
+        <v>81</v>
       </c>
       <c r="E11" s="17">
         <v>0.3</v>
@@ -3388,7 +3362,7 @@
       </c>
       <c r="G11" s="33">
         <f t="shared" si="0"/>
-        <v>7.4699999999999989</v>
+        <v>7.29</v>
       </c>
       <c r="H11" s="17"/>
       <c r="I11" s="17"/>
@@ -3404,8 +3378,8 @@
         <v>1</v>
       </c>
       <c r="D12" s="33">
-        <f>50+30+2+50+38</f>
-        <v>170</v>
+        <f>50+30+2+50+38-20</f>
+        <v>150</v>
       </c>
       <c r="E12" s="17">
         <v>0.3</v>
@@ -3415,7 +3389,7 @@
       </c>
       <c r="G12" s="33">
         <f t="shared" si="0"/>
-        <v>15.299999999999999</v>
+        <v>13.5</v>
       </c>
       <c r="H12" s="17"/>
       <c r="I12" s="17"/>
@@ -3431,8 +3405,8 @@
         <v>1</v>
       </c>
       <c r="D13" s="33">
-        <f>36+35</f>
-        <v>71</v>
+        <f>36+35-15</f>
+        <v>56</v>
       </c>
       <c r="E13" s="17">
         <v>0.3</v>
@@ -3442,7 +3416,7 @@
       </c>
       <c r="G13" s="33">
         <f t="shared" ref="G13" si="1">PRODUCT(C13:F13)</f>
-        <v>6.39</v>
+        <v>5.04</v>
       </c>
       <c r="H13" s="17"/>
       <c r="I13" s="17"/>
@@ -3458,7 +3432,8 @@
         <v>1</v>
       </c>
       <c r="D14" s="33">
-        <v>23</v>
+        <f>23-15</f>
+        <v>8</v>
       </c>
       <c r="E14" s="17">
         <v>0.3</v>
@@ -3468,7 +3443,7 @@
       </c>
       <c r="G14" s="33">
         <f t="shared" ref="G14" si="2">PRODUCT(C14:F14)</f>
-        <v>2.0699999999999998</v>
+        <v>0.72</v>
       </c>
       <c r="H14" s="17"/>
       <c r="I14" s="17"/>
@@ -3484,8 +3459,8 @@
         <v>1</v>
       </c>
       <c r="D15" s="33">
-        <f>36+11+23+30-0.7+50+25+30.7-8+8+50+9+50+50+40+20+50+50+42</f>
-        <v>566</v>
+        <f>36+11+23+30-0.7+50+25+30.7-8+8+50+9+50+50+40+20+50+50+42-3-40-5</f>
+        <v>518</v>
       </c>
       <c r="E15" s="17">
         <v>0.3</v>
@@ -3495,7 +3470,7 @@
       </c>
       <c r="G15" s="33">
         <f t="shared" ref="G15" si="3">PRODUCT(C15:F15)</f>
-        <v>50.939999999999991</v>
+        <v>46.62</v>
       </c>
       <c r="H15" s="17"/>
       <c r="I15" s="17"/>
@@ -3513,7 +3488,7 @@
       <c r="F16" s="5"/>
       <c r="G16" s="41">
         <f>SUM(G10:G15)</f>
-        <v>97.289999999999992</v>
+        <v>88.199999999999989</v>
       </c>
       <c r="H16" s="7" t="s">
         <v>29</v>
@@ -3523,7 +3498,7 @@
       </c>
       <c r="J16" s="41">
         <f>G16*I16</f>
-        <v>93695.134499999986</v>
+        <v>84941.00999999998</v>
       </c>
       <c r="K16" s="5"/>
     </row>
@@ -3563,17 +3538,17 @@
         <v>37</v>
       </c>
       <c r="C19" s="17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D19" s="33">
         <f>(SUM(D10:D15))-1*3</f>
-        <v>1078</v>
+        <v>977</v>
       </c>
       <c r="E19" s="17"/>
       <c r="F19" s="17"/>
       <c r="G19" s="33">
         <f t="shared" ref="G19" si="4">PRODUCT(C19:F19)</f>
-        <v>1078</v>
+        <v>0</v>
       </c>
       <c r="H19" s="17"/>
       <c r="I19" s="17"/>
@@ -3591,7 +3566,7 @@
       <c r="F20" s="5"/>
       <c r="G20" s="41">
         <f>SUM(G19:G19)</f>
-        <v>1078</v>
+        <v>0</v>
       </c>
       <c r="H20" s="7" t="s">
         <v>42</v>
@@ -3602,7 +3577,7 @@
       </c>
       <c r="J20" s="41">
         <f>G20*I20</f>
-        <v>5734.4209999999994</v>
+        <v>0</v>
       </c>
       <c r="K20" s="5"/>
     </row>
@@ -3651,7 +3626,6 @@
         <v>1</v>
       </c>
       <c r="D23" s="33">
-        <f>D10</f>
         <v>168</v>
       </c>
       <c r="E23" s="17">
@@ -3679,18 +3653,17 @@
         <v>1</v>
       </c>
       <c r="D24" s="33">
-        <f t="shared" ref="D24:D28" si="5">D11</f>
         <v>83</v>
       </c>
       <c r="E24" s="17">
         <v>0.33800000000000002</v>
       </c>
       <c r="F24" s="17">
-        <f t="shared" ref="F24:F25" si="6">C24*D24*E24</f>
+        <f t="shared" ref="F24:F25" si="5">C24*D24*E24</f>
         <v>28.054000000000002</v>
       </c>
       <c r="G24" s="33">
-        <f t="shared" ref="G24:G25" si="7">F24</f>
+        <f t="shared" ref="G24:G25" si="6">F24</f>
         <v>28.054000000000002</v>
       </c>
       <c r="H24" s="17"/>
@@ -3707,18 +3680,17 @@
         <v>1</v>
       </c>
       <c r="D25" s="33">
-        <f t="shared" si="5"/>
         <v>170</v>
       </c>
       <c r="E25" s="17">
         <v>0.33800000000000002</v>
       </c>
       <c r="F25" s="17">
+        <f t="shared" si="5"/>
+        <v>57.46</v>
+      </c>
+      <c r="G25" s="33">
         <f t="shared" si="6"/>
-        <v>57.46</v>
-      </c>
-      <c r="G25" s="33">
-        <f t="shared" si="7"/>
         <v>57.46</v>
       </c>
       <c r="H25" s="17"/>
@@ -3735,18 +3707,17 @@
         <v>1</v>
       </c>
       <c r="D26" s="33">
-        <f t="shared" si="5"/>
         <v>71</v>
       </c>
       <c r="E26" s="17">
         <v>0.33800000000000002</v>
       </c>
       <c r="F26" s="17">
-        <f t="shared" ref="F26:F28" si="8">C26*D26*E26</f>
+        <f t="shared" ref="F26:F28" si="7">C26*D26*E26</f>
         <v>23.998000000000001</v>
       </c>
       <c r="G26" s="33">
-        <f t="shared" ref="G26:G28" si="9">F26</f>
+        <f t="shared" ref="G26:G28" si="8">F26</f>
         <v>23.998000000000001</v>
       </c>
       <c r="H26" s="17"/>
@@ -3763,18 +3734,17 @@
         <v>1</v>
       </c>
       <c r="D27" s="33">
-        <f t="shared" si="5"/>
         <v>23</v>
       </c>
       <c r="E27" s="17">
         <v>0.33800000000000002</v>
       </c>
       <c r="F27" s="17">
+        <f t="shared" si="7"/>
+        <v>7.7740000000000009</v>
+      </c>
+      <c r="G27" s="33">
         <f t="shared" si="8"/>
-        <v>7.7740000000000009</v>
-      </c>
-      <c r="G27" s="33">
-        <f t="shared" si="9"/>
         <v>7.7740000000000009</v>
       </c>
       <c r="H27" s="17"/>
@@ -3791,19 +3761,18 @@
         <v>1</v>
       </c>
       <c r="D28" s="33">
-        <f t="shared" si="5"/>
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="E28" s="17">
         <v>0.33800000000000002</v>
       </c>
       <c r="F28" s="17">
+        <f t="shared" si="7"/>
+        <v>190.97</v>
+      </c>
+      <c r="G28" s="33">
         <f t="shared" si="8"/>
-        <v>191.30800000000002</v>
-      </c>
-      <c r="G28" s="33">
-        <f t="shared" si="9"/>
-        <v>191.30800000000002</v>
+        <v>190.97</v>
       </c>
       <c r="H28" s="17"/>
       <c r="I28" s="17"/>
@@ -3821,7 +3790,7 @@
       <c r="F29" s="5"/>
       <c r="G29" s="6">
         <f>SUM(G23:G28)</f>
-        <v>365.37800000000004</v>
+        <v>365.03999999999996</v>
       </c>
       <c r="H29" s="7" t="s">
         <v>33</v>
@@ -3831,7 +3800,7 @@
       </c>
       <c r="J29" s="18">
         <f>G29*I29</f>
-        <v>104863.48600000002</v>
+        <v>104766.48</v>
       </c>
       <c r="K29" s="5"/>
     </row>
@@ -3849,7 +3818,7 @@
       <c r="I30" s="17"/>
       <c r="J30" s="18">
         <f>0.13*J29</f>
-        <v>13632.253180000003</v>
+        <v>13619.642400000001</v>
       </c>
       <c r="K30" s="17"/>
     </row>
@@ -3897,7 +3866,7 @@
       <c r="E33" s="17"/>
       <c r="F33" s="17"/>
       <c r="G33" s="33">
-        <f t="shared" ref="G33" si="10">PRODUCT(C33:F33)</f>
+        <f t="shared" ref="G33" si="9">PRODUCT(C33:F33)</f>
         <v>3</v>
       </c>
       <c r="H33" s="17"/>
@@ -3969,24 +3938,24 @@
         <v>44</v>
       </c>
       <c r="C37" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="5"/>
       <c r="F37" s="5"/>
       <c r="G37" s="41">
-        <f t="shared" ref="G37" si="11">PRODUCT(C37:F37)</f>
-        <v>0</v>
+        <f t="shared" ref="G37" si="10">PRODUCT(C37:F37)</f>
+        <v>1</v>
       </c>
       <c r="H37" s="7" t="s">
         <v>45</v>
       </c>
       <c r="I37" s="6">
-        <v>7000</v>
+        <v>3100</v>
       </c>
       <c r="J37" s="41">
         <f>G37*I37</f>
-        <v>0</v>
+        <v>3100</v>
       </c>
       <c r="K37" s="5"/>
     </row>
@@ -4017,7 +3986,7 @@
       <c r="E39" s="5"/>
       <c r="F39" s="5"/>
       <c r="G39" s="7">
-        <f t="shared" ref="G39" si="12">PRODUCT(C39:F39)</f>
+        <f t="shared" ref="G39" si="11">PRODUCT(C39:F39)</f>
         <v>1</v>
       </c>
       <c r="H39" s="7" t="s">
@@ -4059,7 +4028,7 @@
       <c r="I41" s="18"/>
       <c r="J41" s="18">
         <f>SUM(J9:J39)</f>
-        <v>219957.57467999999</v>
+        <v>208459.4124</v>
       </c>
       <c r="K41" s="25"/>
     </row>
@@ -4068,11 +4037,11 @@
       <c r="B43" s="27" t="s">
         <v>55</v>
       </c>
-      <c r="C43" s="43">
+      <c r="C43" s="81">
         <f>J41</f>
-        <v>219957.57467999999</v>
-      </c>
-      <c r="D43" s="44"/>
+        <v>208459.4124</v>
+      </c>
+      <c r="D43" s="82"/>
       <c r="E43" s="9">
         <v>100</v>
       </c>
@@ -4087,49 +4056,49 @@
       <c r="B44" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="C44" s="47">
+      <c r="C44" s="85">
         <v>300000</v>
       </c>
-      <c r="D44" s="48"/>
+      <c r="D44" s="86"/>
       <c r="E44" s="9"/>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B45" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="C45" s="47">
-        <f>C44-C47-C48</f>
-        <v>285000</v>
-      </c>
-      <c r="D45" s="48"/>
+      <c r="C45" s="85">
+        <f>84.79%*C43</f>
+        <v>176752.73577396001</v>
+      </c>
+      <c r="D45" s="86"/>
       <c r="E45" s="9">
         <f>C45/C43*100</f>
-        <v>129.57044121559596</v>
+        <v>84.79</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B46" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="C46" s="49">
+      <c r="C46" s="87">
         <f>C43-C45</f>
-        <v>-65042.425320000009</v>
-      </c>
-      <c r="D46" s="49"/>
+        <v>31706.676626039989</v>
+      </c>
+      <c r="D46" s="87"/>
       <c r="E46" s="9">
         <f>100-E45</f>
-        <v>-29.570441215595963</v>
+        <v>15.209999999999994</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B47" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="C47" s="43">
+      <c r="C47" s="81">
         <f>C44*0.03</f>
         <v>9000</v>
       </c>
-      <c r="D47" s="44"/>
+      <c r="D47" s="82"/>
       <c r="E47" s="9">
         <v>3</v>
       </c>
@@ -4138,17 +4107,24 @@
       <c r="B48" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="C48" s="43">
+      <c r="C48" s="81">
         <f>C44*0.02</f>
         <v>6000</v>
       </c>
-      <c r="D48" s="44"/>
+      <c r="D48" s="82"/>
       <c r="E48" s="9">
         <v>2</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="H6:K6"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A4:K4"/>
+    <mergeCell ref="A5:K5"/>
     <mergeCell ref="C47:D47"/>
     <mergeCell ref="C48:D48"/>
     <mergeCell ref="A7:F7"/>
@@ -4157,13 +4133,6 @@
     <mergeCell ref="C44:D44"/>
     <mergeCell ref="C45:D45"/>
     <mergeCell ref="C46:D46"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A4:K4"/>
-    <mergeCell ref="A5:K5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="H6:K6"/>
   </mergeCells>
   <phoneticPr fontId="16" type="noConversion"/>
   <pageMargins left="0.70866141732283505" right="0.70866141732283505" top="0.74803149606299202" bottom="0.74803149606299202" header="0.31496062992126" footer="0.31496062992126"/>
@@ -4175,6 +4144,1008 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89642F61-87AB-4749-B1E7-6713FC71D00F}">
+  <dimension ref="A1:K48"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="4.7109375" style="19" customWidth="1"/>
+    <col min="2" max="2" width="30.85546875" style="19" customWidth="1"/>
+    <col min="3" max="3" width="4.42578125" style="19" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.42578125" style="19" customWidth="1"/>
+    <col min="5" max="5" width="8.5703125" style="19" customWidth="1"/>
+    <col min="6" max="6" width="7.28515625" style="19" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" style="19"/>
+    <col min="8" max="8" width="5" style="19" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.5703125" style="19" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="10.7109375" style="19" hidden="1" customWidth="1"/>
+    <col min="11" max="16384" width="9.140625" style="19"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" s="77" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="77"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="77"/>
+      <c r="G1" s="77"/>
+      <c r="H1" s="77"/>
+      <c r="I1" s="77"/>
+      <c r="J1" s="77"/>
+      <c r="K1" s="77"/>
+    </row>
+    <row r="2" spans="1:11" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2" s="78" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
+      <c r="K2" s="78"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="79" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="79"/>
+      <c r="C3" s="79"/>
+      <c r="D3" s="79"/>
+      <c r="E3" s="79"/>
+      <c r="F3" s="79"/>
+      <c r="G3" s="79"/>
+      <c r="H3" s="79"/>
+      <c r="I3" s="79"/>
+      <c r="J3" s="79"/>
+      <c r="K3" s="79"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" s="79" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="79"/>
+      <c r="C4" s="79"/>
+      <c r="D4" s="79"/>
+      <c r="E4" s="79"/>
+      <c r="F4" s="79"/>
+      <c r="G4" s="79"/>
+      <c r="H4" s="79"/>
+      <c r="I4" s="79"/>
+      <c r="J4" s="79"/>
+      <c r="K4" s="79"/>
+    </row>
+    <row r="5" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A5" s="80" t="s">
+        <v>69</v>
+      </c>
+      <c r="B5" s="80"/>
+      <c r="C5" s="80"/>
+      <c r="D5" s="80"/>
+      <c r="E5" s="80"/>
+      <c r="F5" s="80"/>
+      <c r="G5" s="80"/>
+      <c r="H5" s="80"/>
+      <c r="I5" s="80"/>
+      <c r="J5" s="80"/>
+      <c r="K5" s="80"/>
+    </row>
+    <row r="6" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A6" s="67" t="s">
+        <v>46</v>
+      </c>
+      <c r="B6" s="67"/>
+      <c r="C6" s="67"/>
+      <c r="D6" s="67"/>
+      <c r="E6" s="67"/>
+      <c r="F6" s="67"/>
+      <c r="G6" s="10"/>
+      <c r="I6" s="88"/>
+      <c r="J6" s="88"/>
+      <c r="K6" s="44" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="83" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7" s="83"/>
+      <c r="C7" s="83"/>
+      <c r="D7" s="83"/>
+      <c r="E7" s="83"/>
+      <c r="F7" s="83"/>
+      <c r="G7" s="11"/>
+      <c r="I7" s="89"/>
+      <c r="J7" s="89"/>
+      <c r="K7" s="43" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="G8" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="H8" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="I8" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="J8" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="K8" s="15" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="33" x14ac:dyDescent="0.25">
+      <c r="A9" s="16">
+        <v>1</v>
+      </c>
+      <c r="B9" s="39" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9" s="17"/>
+      <c r="D9" s="17"/>
+      <c r="E9" s="17"/>
+      <c r="F9" s="17"/>
+      <c r="G9" s="17"/>
+      <c r="H9" s="17"/>
+      <c r="I9" s="17"/>
+      <c r="J9" s="18"/>
+      <c r="K9" s="17"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" s="16"/>
+      <c r="B10" s="32" t="s">
+        <v>50</v>
+      </c>
+      <c r="C10" s="17">
+        <v>1</v>
+      </c>
+      <c r="D10" s="33">
+        <f>90+38+40-1</f>
+        <v>167</v>
+      </c>
+      <c r="E10" s="17">
+        <v>0.3</v>
+      </c>
+      <c r="F10" s="17">
+        <v>0.3</v>
+      </c>
+      <c r="G10" s="33">
+        <f t="shared" ref="G10:G15" si="0">PRODUCT(C10:F10)</f>
+        <v>15.03</v>
+      </c>
+      <c r="H10" s="17"/>
+      <c r="I10" s="17"/>
+      <c r="J10" s="18"/>
+      <c r="K10" s="17"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" s="16"/>
+      <c r="B11" s="32" t="s">
+        <v>49</v>
+      </c>
+      <c r="C11" s="17">
+        <v>1</v>
+      </c>
+      <c r="D11" s="33">
+        <f>40+43-2</f>
+        <v>81</v>
+      </c>
+      <c r="E11" s="17">
+        <v>0.3</v>
+      </c>
+      <c r="F11" s="17">
+        <v>0.3</v>
+      </c>
+      <c r="G11" s="33">
+        <f t="shared" si="0"/>
+        <v>7.29</v>
+      </c>
+      <c r="H11" s="17"/>
+      <c r="I11" s="17"/>
+      <c r="J11" s="18"/>
+      <c r="K11" s="17"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" s="16"/>
+      <c r="B12" s="32" t="s">
+        <v>51</v>
+      </c>
+      <c r="C12" s="17">
+        <v>1</v>
+      </c>
+      <c r="D12" s="33">
+        <f>50+30+2+50+38-20</f>
+        <v>150</v>
+      </c>
+      <c r="E12" s="17">
+        <v>0.3</v>
+      </c>
+      <c r="F12" s="17">
+        <v>0.3</v>
+      </c>
+      <c r="G12" s="33">
+        <f t="shared" si="0"/>
+        <v>13.5</v>
+      </c>
+      <c r="H12" s="17"/>
+      <c r="I12" s="17"/>
+      <c r="J12" s="18"/>
+      <c r="K12" s="17"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" s="16"/>
+      <c r="B13" s="32" t="s">
+        <v>52</v>
+      </c>
+      <c r="C13" s="17">
+        <v>1</v>
+      </c>
+      <c r="D13" s="33">
+        <f>36+35-15</f>
+        <v>56</v>
+      </c>
+      <c r="E13" s="17">
+        <v>0.3</v>
+      </c>
+      <c r="F13" s="17">
+        <v>0.3</v>
+      </c>
+      <c r="G13" s="33">
+        <f t="shared" si="0"/>
+        <v>5.04</v>
+      </c>
+      <c r="H13" s="17"/>
+      <c r="I13" s="17"/>
+      <c r="J13" s="18"/>
+      <c r="K13" s="17"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" s="16"/>
+      <c r="B14" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="C14" s="17">
+        <v>1</v>
+      </c>
+      <c r="D14" s="33">
+        <f>23-15</f>
+        <v>8</v>
+      </c>
+      <c r="E14" s="17">
+        <v>0.3</v>
+      </c>
+      <c r="F14" s="17">
+        <v>0.3</v>
+      </c>
+      <c r="G14" s="33">
+        <f t="shared" si="0"/>
+        <v>0.72</v>
+      </c>
+      <c r="H14" s="17"/>
+      <c r="I14" s="17"/>
+      <c r="J14" s="18"/>
+      <c r="K14" s="17"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" s="16"/>
+      <c r="B15" s="32" t="s">
+        <v>54</v>
+      </c>
+      <c r="C15" s="17">
+        <v>1</v>
+      </c>
+      <c r="D15" s="33">
+        <f>36+11+23+30-0.7+50+25+30.7-8+8+50+9+50+50+40+20+50+50+42-3-40-5</f>
+        <v>518</v>
+      </c>
+      <c r="E15" s="17">
+        <v>0.3</v>
+      </c>
+      <c r="F15" s="17">
+        <v>0.3</v>
+      </c>
+      <c r="G15" s="33">
+        <f t="shared" si="0"/>
+        <v>46.62</v>
+      </c>
+      <c r="H15" s="17"/>
+      <c r="I15" s="17"/>
+      <c r="J15" s="18"/>
+      <c r="K15" s="17"/>
+    </row>
+    <row r="16" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="2"/>
+      <c r="B16" s="40" t="s">
+        <v>28</v>
+      </c>
+      <c r="C16" s="3"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="41">
+        <f>SUM(G10:G15)</f>
+        <v>88.199999999999989</v>
+      </c>
+      <c r="H16" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="I16" s="6">
+        <v>963.05</v>
+      </c>
+      <c r="J16" s="41">
+        <f>G16*I16</f>
+        <v>84941.00999999998</v>
+      </c>
+      <c r="K16" s="5"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17" s="16"/>
+      <c r="B17" s="32"/>
+      <c r="C17" s="17"/>
+      <c r="D17" s="17"/>
+      <c r="E17" s="17"/>
+      <c r="F17" s="17"/>
+      <c r="G17" s="17"/>
+      <c r="H17" s="17"/>
+      <c r="I17" s="17"/>
+      <c r="J17" s="18"/>
+      <c r="K17" s="17"/>
+    </row>
+    <row r="18" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A18" s="16">
+        <v>2</v>
+      </c>
+      <c r="B18" s="39" t="s">
+        <v>41</v>
+      </c>
+      <c r="C18" s="17"/>
+      <c r="D18" s="17"/>
+      <c r="E18" s="17"/>
+      <c r="F18" s="17"/>
+      <c r="G18" s="17"/>
+      <c r="H18" s="17"/>
+      <c r="I18" s="17"/>
+      <c r="J18" s="17"/>
+      <c r="K18" s="17"/>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19" s="16"/>
+      <c r="B19" s="32" t="s">
+        <v>37</v>
+      </c>
+      <c r="C19" s="17">
+        <v>0</v>
+      </c>
+      <c r="D19" s="33">
+        <f>(SUM(D10:D15))-1*3</f>
+        <v>977</v>
+      </c>
+      <c r="E19" s="17"/>
+      <c r="F19" s="17"/>
+      <c r="G19" s="33">
+        <f t="shared" ref="G19" si="1">PRODUCT(C19:F19)</f>
+        <v>0</v>
+      </c>
+      <c r="H19" s="17"/>
+      <c r="I19" s="17"/>
+      <c r="J19" s="18"/>
+      <c r="K19" s="17"/>
+    </row>
+    <row r="20" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="2"/>
+      <c r="B20" s="40" t="s">
+        <v>28</v>
+      </c>
+      <c r="C20" s="3"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="41">
+        <f>SUM(G19:G19)</f>
+        <v>0</v>
+      </c>
+      <c r="H20" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="I20" s="6">
+        <f>5319.5/1000</f>
+        <v>5.3194999999999997</v>
+      </c>
+      <c r="J20" s="41">
+        <f>G20*I20</f>
+        <v>0</v>
+      </c>
+      <c r="K20" s="5"/>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21" s="16"/>
+      <c r="B21" s="39"/>
+      <c r="C21" s="17"/>
+      <c r="D21" s="17"/>
+      <c r="E21" s="17"/>
+      <c r="F21" s="17"/>
+      <c r="G21" s="17"/>
+      <c r="H21" s="17"/>
+      <c r="I21" s="17"/>
+      <c r="J21" s="17"/>
+      <c r="K21" s="17"/>
+    </row>
+    <row r="22" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="A22" s="16">
+        <v>3</v>
+      </c>
+      <c r="B22" s="36" t="s">
+        <v>30</v>
+      </c>
+      <c r="C22" s="17"/>
+      <c r="D22" s="37" t="s">
+        <v>27</v>
+      </c>
+      <c r="E22" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="F22" s="37" t="s">
+        <v>32</v>
+      </c>
+      <c r="G22" s="17"/>
+      <c r="H22" s="17"/>
+      <c r="I22" s="17"/>
+      <c r="J22" s="18"/>
+      <c r="K22" s="17"/>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A23" s="16"/>
+      <c r="B23" s="32" t="s">
+        <v>50</v>
+      </c>
+      <c r="C23" s="17">
+        <v>1</v>
+      </c>
+      <c r="D23" s="33">
+        <v>168</v>
+      </c>
+      <c r="E23" s="17">
+        <v>0.33800000000000002</v>
+      </c>
+      <c r="F23" s="17">
+        <f>C23*D23*E23</f>
+        <v>56.784000000000006</v>
+      </c>
+      <c r="G23" s="33">
+        <f>F23</f>
+        <v>56.784000000000006</v>
+      </c>
+      <c r="H23" s="17"/>
+      <c r="I23" s="17"/>
+      <c r="J23" s="18"/>
+      <c r="K23" s="17"/>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A24" s="16"/>
+      <c r="B24" s="32" t="s">
+        <v>49</v>
+      </c>
+      <c r="C24" s="17">
+        <v>1</v>
+      </c>
+      <c r="D24" s="33">
+        <v>83</v>
+      </c>
+      <c r="E24" s="17">
+        <v>0.33800000000000002</v>
+      </c>
+      <c r="F24" s="17">
+        <f t="shared" ref="F24:F28" si="2">C24*D24*E24</f>
+        <v>28.054000000000002</v>
+      </c>
+      <c r="G24" s="33">
+        <f t="shared" ref="G24:G28" si="3">F24</f>
+        <v>28.054000000000002</v>
+      </c>
+      <c r="H24" s="17"/>
+      <c r="I24" s="17"/>
+      <c r="J24" s="18"/>
+      <c r="K24" s="17"/>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A25" s="16"/>
+      <c r="B25" s="32" t="s">
+        <v>51</v>
+      </c>
+      <c r="C25" s="17">
+        <v>1</v>
+      </c>
+      <c r="D25" s="33">
+        <v>170</v>
+      </c>
+      <c r="E25" s="17">
+        <v>0.33800000000000002</v>
+      </c>
+      <c r="F25" s="17">
+        <f t="shared" si="2"/>
+        <v>57.46</v>
+      </c>
+      <c r="G25" s="33">
+        <f t="shared" si="3"/>
+        <v>57.46</v>
+      </c>
+      <c r="H25" s="17"/>
+      <c r="I25" s="17"/>
+      <c r="J25" s="18"/>
+      <c r="K25" s="17"/>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A26" s="16"/>
+      <c r="B26" s="32" t="s">
+        <v>52</v>
+      </c>
+      <c r="C26" s="17">
+        <v>1</v>
+      </c>
+      <c r="D26" s="33">
+        <v>71</v>
+      </c>
+      <c r="E26" s="17">
+        <v>0.33800000000000002</v>
+      </c>
+      <c r="F26" s="17">
+        <f t="shared" si="2"/>
+        <v>23.998000000000001</v>
+      </c>
+      <c r="G26" s="33">
+        <f t="shared" si="3"/>
+        <v>23.998000000000001</v>
+      </c>
+      <c r="H26" s="17"/>
+      <c r="I26" s="17"/>
+      <c r="J26" s="18"/>
+      <c r="K26" s="17"/>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A27" s="16"/>
+      <c r="B27" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="C27" s="17">
+        <v>1</v>
+      </c>
+      <c r="D27" s="33">
+        <v>23</v>
+      </c>
+      <c r="E27" s="17">
+        <v>0.33800000000000002</v>
+      </c>
+      <c r="F27" s="17">
+        <f t="shared" si="2"/>
+        <v>7.7740000000000009</v>
+      </c>
+      <c r="G27" s="33">
+        <f t="shared" si="3"/>
+        <v>7.7740000000000009</v>
+      </c>
+      <c r="H27" s="17"/>
+      <c r="I27" s="17"/>
+      <c r="J27" s="18"/>
+      <c r="K27" s="17"/>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A28" s="16"/>
+      <c r="B28" s="32" t="s">
+        <v>54</v>
+      </c>
+      <c r="C28" s="17">
+        <v>1</v>
+      </c>
+      <c r="D28" s="33">
+        <v>565</v>
+      </c>
+      <c r="E28" s="17">
+        <v>0.33800000000000002</v>
+      </c>
+      <c r="F28" s="17">
+        <f t="shared" si="2"/>
+        <v>190.97</v>
+      </c>
+      <c r="G28" s="33">
+        <f t="shared" si="3"/>
+        <v>190.97</v>
+      </c>
+      <c r="H28" s="17"/>
+      <c r="I28" s="17"/>
+      <c r="J28" s="18"/>
+      <c r="K28" s="17"/>
+    </row>
+    <row r="29" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="2"/>
+      <c r="B29" s="34" t="s">
+        <v>16</v>
+      </c>
+      <c r="C29" s="3"/>
+      <c r="D29" s="4"/>
+      <c r="E29" s="5"/>
+      <c r="F29" s="5"/>
+      <c r="G29" s="6">
+        <f>SUM(G23:G28)</f>
+        <v>365.03999999999996</v>
+      </c>
+      <c r="H29" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="I29" s="6">
+        <v>287</v>
+      </c>
+      <c r="J29" s="18">
+        <f>G29*I29</f>
+        <v>104766.48</v>
+      </c>
+      <c r="K29" s="5"/>
+    </row>
+    <row r="30" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="16"/>
+      <c r="B30" s="32" t="s">
+        <v>36</v>
+      </c>
+      <c r="C30" s="17"/>
+      <c r="D30" s="17"/>
+      <c r="E30" s="17"/>
+      <c r="F30" s="17"/>
+      <c r="G30" s="17"/>
+      <c r="H30" s="17"/>
+      <c r="I30" s="17"/>
+      <c r="J30" s="18">
+        <f>0.13*J29</f>
+        <v>13619.642400000001</v>
+      </c>
+      <c r="K30" s="17"/>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A31" s="16"/>
+      <c r="B31" s="17"/>
+      <c r="C31" s="17"/>
+      <c r="D31" s="17"/>
+      <c r="E31" s="17"/>
+      <c r="F31" s="17"/>
+      <c r="G31" s="17"/>
+      <c r="H31" s="17"/>
+      <c r="I31" s="17"/>
+      <c r="J31" s="17"/>
+      <c r="K31" s="17"/>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A32" s="16">
+        <v>4</v>
+      </c>
+      <c r="B32" s="39" t="s">
+        <v>43</v>
+      </c>
+      <c r="C32" s="17"/>
+      <c r="D32" s="17"/>
+      <c r="E32" s="17"/>
+      <c r="F32" s="17"/>
+      <c r="G32" s="17"/>
+      <c r="H32" s="17"/>
+      <c r="I32" s="17"/>
+      <c r="J32" s="17"/>
+      <c r="K32" s="17"/>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A33" s="16"/>
+      <c r="B33" s="32" t="s">
+        <v>37</v>
+      </c>
+      <c r="C33" s="17">
+        <v>1</v>
+      </c>
+      <c r="D33" s="33">
+        <v>3</v>
+      </c>
+      <c r="E33" s="17"/>
+      <c r="F33" s="17"/>
+      <c r="G33" s="33">
+        <f t="shared" ref="G33" si="4">PRODUCT(C33:F33)</f>
+        <v>3</v>
+      </c>
+      <c r="H33" s="17"/>
+      <c r="I33" s="17"/>
+      <c r="J33" s="18"/>
+      <c r="K33" s="17"/>
+    </row>
+    <row r="34" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="2"/>
+      <c r="B34" s="40" t="s">
+        <v>28</v>
+      </c>
+      <c r="C34" s="3"/>
+      <c r="D34" s="4"/>
+      <c r="E34" s="5"/>
+      <c r="F34" s="5"/>
+      <c r="G34" s="41">
+        <f>SUM(G33:G33)</f>
+        <v>3</v>
+      </c>
+      <c r="H34" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="I34" s="6">
+        <v>452</v>
+      </c>
+      <c r="J34" s="41">
+        <f>G34*I34</f>
+        <v>1356</v>
+      </c>
+      <c r="K34" s="5"/>
+    </row>
+    <row r="35" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="16"/>
+      <c r="B35" s="32" t="s">
+        <v>36</v>
+      </c>
+      <c r="C35" s="17"/>
+      <c r="D35" s="17"/>
+      <c r="E35" s="17"/>
+      <c r="F35" s="17"/>
+      <c r="G35" s="17"/>
+      <c r="H35" s="17"/>
+      <c r="I35" s="17"/>
+      <c r="J35" s="18">
+        <f>0.13*J34</f>
+        <v>176.28</v>
+      </c>
+      <c r="K35" s="17"/>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A36" s="16"/>
+      <c r="B36" s="39"/>
+      <c r="C36" s="17"/>
+      <c r="D36" s="17"/>
+      <c r="E36" s="17"/>
+      <c r="F36" s="17"/>
+      <c r="G36" s="17"/>
+      <c r="H36" s="17"/>
+      <c r="I36" s="17"/>
+      <c r="J36" s="17"/>
+      <c r="K36" s="17"/>
+    </row>
+    <row r="37" spans="1:11" s="35" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A37" s="2">
+        <v>5</v>
+      </c>
+      <c r="B37" s="42" t="s">
+        <v>44</v>
+      </c>
+      <c r="C37" s="3">
+        <v>1</v>
+      </c>
+      <c r="D37" s="4"/>
+      <c r="E37" s="5"/>
+      <c r="F37" s="5"/>
+      <c r="G37" s="41">
+        <f t="shared" ref="G37" si="5">PRODUCT(C37:F37)</f>
+        <v>1</v>
+      </c>
+      <c r="H37" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="I37" s="6">
+        <v>3100</v>
+      </c>
+      <c r="J37" s="41">
+        <f>G37*I37</f>
+        <v>3100</v>
+      </c>
+      <c r="K37" s="5"/>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A38" s="16"/>
+      <c r="B38" s="39"/>
+      <c r="C38" s="17"/>
+      <c r="D38" s="17"/>
+      <c r="E38" s="17"/>
+      <c r="F38" s="17"/>
+      <c r="G38" s="17"/>
+      <c r="H38" s="17"/>
+      <c r="I38" s="17"/>
+      <c r="J38" s="17"/>
+      <c r="K38" s="17"/>
+    </row>
+    <row r="39" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="2">
+        <v>6</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C39" s="3">
+        <v>1</v>
+      </c>
+      <c r="D39" s="4"/>
+      <c r="E39" s="5"/>
+      <c r="F39" s="5"/>
+      <c r="G39" s="7">
+        <f t="shared" ref="G39" si="6">PRODUCT(C39:F39)</f>
+        <v>1</v>
+      </c>
+      <c r="H39" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="I39" s="6">
+        <v>500</v>
+      </c>
+      <c r="J39" s="7">
+        <f>G39*I39</f>
+        <v>500</v>
+      </c>
+      <c r="K39" s="5"/>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A40" s="2"/>
+      <c r="B40" s="8"/>
+      <c r="C40" s="3"/>
+      <c r="D40" s="4"/>
+      <c r="E40" s="5"/>
+      <c r="F40" s="5"/>
+      <c r="G40" s="6"/>
+      <c r="H40" s="7"/>
+      <c r="I40" s="6"/>
+      <c r="J40" s="18"/>
+      <c r="K40" s="5"/>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A41" s="21"/>
+      <c r="B41" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="C41" s="23"/>
+      <c r="D41" s="24"/>
+      <c r="E41" s="24"/>
+      <c r="F41" s="24"/>
+      <c r="G41" s="18"/>
+      <c r="H41" s="18"/>
+      <c r="I41" s="18"/>
+      <c r="J41" s="18">
+        <f>SUM(J9:J39)</f>
+        <v>208459.4124</v>
+      </c>
+      <c r="K41" s="25"/>
+    </row>
+    <row r="43" spans="1:11" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="26"/>
+      <c r="B43" s="27" t="s">
+        <v>55</v>
+      </c>
+      <c r="C43" s="81">
+        <f>J41</f>
+        <v>208459.4124</v>
+      </c>
+      <c r="D43" s="82"/>
+      <c r="E43" s="9">
+        <v>100</v>
+      </c>
+      <c r="F43" s="26"/>
+      <c r="G43" s="28"/>
+      <c r="H43" s="26"/>
+      <c r="I43" s="29"/>
+      <c r="J43" s="30"/>
+      <c r="K43" s="31"/>
+    </row>
+    <row r="44" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B44" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="C44" s="85">
+        <v>300000</v>
+      </c>
+      <c r="D44" s="86"/>
+      <c r="E44" s="9"/>
+    </row>
+    <row r="45" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B45" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="C45" s="85">
+        <f>84.79%*C43</f>
+        <v>176752.73577396001</v>
+      </c>
+      <c r="D45" s="86"/>
+      <c r="E45" s="9">
+        <f>C45/C43*100</f>
+        <v>84.79</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B46" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="C46" s="87">
+        <f>C43-C45</f>
+        <v>31706.676626039989</v>
+      </c>
+      <c r="D46" s="87"/>
+      <c r="E46" s="9">
+        <f>100-E45</f>
+        <v>15.209999999999994</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B47" s="27" t="s">
+        <v>23</v>
+      </c>
+      <c r="C47" s="81">
+        <f>C44*0.03</f>
+        <v>9000</v>
+      </c>
+      <c r="D47" s="82"/>
+      <c r="E47" s="9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B48" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="C48" s="81">
+        <f>C44*0.02</f>
+        <v>6000</v>
+      </c>
+      <c r="D48" s="82"/>
+      <c r="E48" s="9">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="C48:D48"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="C44:D44"/>
+    <mergeCell ref="C45:D45"/>
+    <mergeCell ref="C46:D46"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A4:K4"/>
+    <mergeCell ref="A5:K5"/>
+    <mergeCell ref="A6:F6"/>
+  </mergeCells>
+  <pageMargins left="0.70866141732283505" right="0.70866141732283505" top="0.74803149606299202" bottom="0.74803149606299202" header="0.31496062992126" footer="0.31496062992126"/>
+  <pageSetup paperSize="9" scale="95" orientation="portrait" verticalDpi="1200" r:id="rId1"/>
+  <headerFooter>
+    <oddFooter>&amp;LPrepared By:&amp;CChecked By:&amp;RApproved By:</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0790B604-1950-4F4C-A16C-E1F1668745FE}">
   <dimension ref="A1:S41"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -4195,113 +5166,113 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A1" s="52" t="s">
+      <c r="A1" s="77" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-      <c r="F1" s="52"/>
-      <c r="G1" s="52"/>
-      <c r="H1" s="52"/>
-      <c r="I1" s="52"/>
-      <c r="J1" s="52"/>
-      <c r="K1" s="52"/>
+      <c r="B1" s="77"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="77"/>
+      <c r="G1" s="77"/>
+      <c r="H1" s="77"/>
+      <c r="I1" s="77"/>
+      <c r="J1" s="77"/>
+      <c r="K1" s="77"/>
     </row>
     <row r="2" spans="1:19" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="53" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="53"/>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
-      <c r="I2" s="53"/>
-      <c r="J2" s="53"/>
-      <c r="K2" s="53"/>
+      <c r="A2" s="78" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
+      <c r="K2" s="78"/>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A3" s="54" t="s">
+      <c r="A3" s="79" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="54"/>
-      <c r="C3" s="54"/>
-      <c r="D3" s="54"/>
-      <c r="E3" s="54"/>
-      <c r="F3" s="54"/>
-      <c r="G3" s="54"/>
-      <c r="H3" s="54"/>
-      <c r="I3" s="54"/>
-      <c r="J3" s="54"/>
-      <c r="K3" s="54"/>
+      <c r="B3" s="79"/>
+      <c r="C3" s="79"/>
+      <c r="D3" s="79"/>
+      <c r="E3" s="79"/>
+      <c r="F3" s="79"/>
+      <c r="G3" s="79"/>
+      <c r="H3" s="79"/>
+      <c r="I3" s="79"/>
+      <c r="J3" s="79"/>
+      <c r="K3" s="79"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A4" s="54" t="s">
+      <c r="A4" s="79" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="54"/>
-      <c r="C4" s="54"/>
-      <c r="D4" s="54"/>
-      <c r="E4" s="54"/>
-      <c r="F4" s="54"/>
-      <c r="G4" s="54"/>
-      <c r="H4" s="54"/>
-      <c r="I4" s="54"/>
-      <c r="J4" s="54"/>
-      <c r="K4" s="54"/>
+      <c r="B4" s="79"/>
+      <c r="C4" s="79"/>
+      <c r="D4" s="79"/>
+      <c r="E4" s="79"/>
+      <c r="F4" s="79"/>
+      <c r="G4" s="79"/>
+      <c r="H4" s="79"/>
+      <c r="I4" s="79"/>
+      <c r="J4" s="79"/>
+      <c r="K4" s="79"/>
     </row>
     <row r="5" spans="1:19" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A5" s="55" t="s">
+      <c r="A5" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="55"/>
-      <c r="C5" s="55"/>
-      <c r="D5" s="55"/>
-      <c r="E5" s="55"/>
-      <c r="F5" s="55"/>
-      <c r="G5" s="55"/>
-      <c r="H5" s="55"/>
-      <c r="I5" s="55"/>
-      <c r="J5" s="55"/>
-      <c r="K5" s="55"/>
+      <c r="B5" s="80"/>
+      <c r="C5" s="80"/>
+      <c r="D5" s="80"/>
+      <c r="E5" s="80"/>
+      <c r="F5" s="80"/>
+      <c r="G5" s="80"/>
+      <c r="H5" s="80"/>
+      <c r="I5" s="80"/>
+      <c r="J5" s="80"/>
+      <c r="K5" s="80"/>
     </row>
     <row r="6" spans="1:19" ht="18" x14ac:dyDescent="0.25">
-      <c r="A6" s="50" t="s">
+      <c r="A6" s="67" t="s">
         <v>46</v>
       </c>
-      <c r="B6" s="50"/>
-      <c r="C6" s="50"/>
-      <c r="D6" s="50"/>
-      <c r="E6" s="50"/>
-      <c r="F6" s="50"/>
+      <c r="B6" s="67"/>
+      <c r="C6" s="67"/>
+      <c r="D6" s="67"/>
+      <c r="E6" s="67"/>
+      <c r="F6" s="67"/>
       <c r="G6" s="10"/>
-      <c r="H6" s="51" t="s">
+      <c r="H6" s="76" t="s">
         <v>25</v>
       </c>
-      <c r="I6" s="51"/>
-      <c r="J6" s="51"/>
-      <c r="K6" s="51"/>
+      <c r="I6" s="76"/>
+      <c r="J6" s="76"/>
+      <c r="K6" s="76"/>
     </row>
     <row r="7" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="45" t="s">
+      <c r="A7" s="83" t="s">
         <v>35</v>
       </c>
-      <c r="B7" s="45"/>
-      <c r="C7" s="45"/>
-      <c r="D7" s="45"/>
-      <c r="E7" s="45"/>
-      <c r="F7" s="45"/>
+      <c r="B7" s="83"/>
+      <c r="C7" s="83"/>
+      <c r="D7" s="83"/>
+      <c r="E7" s="83"/>
+      <c r="F7" s="83"/>
       <c r="G7" s="11"/>
-      <c r="H7" s="46" t="s">
+      <c r="H7" s="84" t="s">
         <v>34</v>
       </c>
-      <c r="I7" s="46"/>
-      <c r="J7" s="46"/>
-      <c r="K7" s="46"/>
+      <c r="I7" s="84"/>
+      <c r="J7" s="84"/>
+      <c r="K7" s="84"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
@@ -4926,11 +5897,11 @@
       <c r="B36" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="C36" s="43">
+      <c r="C36" s="81">
         <f>J34</f>
         <v>335761.30499999999</v>
       </c>
-      <c r="D36" s="44"/>
+      <c r="D36" s="82"/>
       <c r="E36" s="9">
         <v>100</v>
       </c>
@@ -4952,21 +5923,21 @@
       <c r="B37" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="C37" s="47">
+      <c r="C37" s="85">
         <v>300000</v>
       </c>
-      <c r="D37" s="48"/>
+      <c r="D37" s="86"/>
       <c r="E37" s="9"/>
     </row>
     <row r="38" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B38" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="C38" s="47">
+      <c r="C38" s="85">
         <f>C37-C40-C41</f>
         <v>285000</v>
       </c>
-      <c r="D38" s="48"/>
+      <c r="D38" s="86"/>
       <c r="E38" s="9">
         <f>C38/C36*100</f>
         <v>84.881728703073762</v>
@@ -4976,11 +5947,11 @@
       <c r="B39" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="C39" s="49">
+      <c r="C39" s="87">
         <f>C36-C38</f>
         <v>50761.304999999993</v>
       </c>
-      <c r="D39" s="49"/>
+      <c r="D39" s="87"/>
       <c r="E39" s="9">
         <f>100-E38</f>
         <v>15.118271296926238</v>
@@ -4990,11 +5961,11 @@
       <c r="B40" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="C40" s="43">
+      <c r="C40" s="81">
         <f>C37*0.03</f>
         <v>9000</v>
       </c>
-      <c r="D40" s="44"/>
+      <c r="D40" s="82"/>
       <c r="E40" s="9">
         <v>3</v>
       </c>
@@ -5003,17 +5974,24 @@
       <c r="B41" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="C41" s="43">
+      <c r="C41" s="81">
         <f>C37*0.02</f>
         <v>6000</v>
       </c>
-      <c r="D41" s="44"/>
+      <c r="D41" s="82"/>
       <c r="E41" s="9">
         <v>2</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="H6:K6"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A4:K4"/>
+    <mergeCell ref="A5:K5"/>
     <mergeCell ref="C40:D40"/>
     <mergeCell ref="C41:D41"/>
     <mergeCell ref="A7:F7"/>
@@ -5022,13 +6000,6 @@
     <mergeCell ref="C37:D37"/>
     <mergeCell ref="C38:D38"/>
     <mergeCell ref="C39:D39"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A4:K4"/>
-    <mergeCell ref="A5:K5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="H6:K6"/>
   </mergeCells>
   <pageMargins left="0.70866141732283505" right="0.70866141732283505" top="0.74803149606299202" bottom="0.74803149606299202" header="0.31496062992126" footer="0.31496062992126"/>
   <pageSetup paperSize="9" scale="80" orientation="portrait" verticalDpi="1200" r:id="rId1"/>

--- a/बजेट माग estimate/नगर बजेट estimate/malsim khanepaani/valuation malsim khanepaani.xlsx
+++ b/बजेट माग estimate/नगर बजेट estimate/malsim khanepaani/valuation malsim khanepaani.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1A6DE53-57E7-4238-B20B-08EC16B7A709}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{814476F4-2FE2-4DF8-A736-479CAE56A123}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="estimate" sheetId="12" r:id="rId1"/>
@@ -747,6 +747,75 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -756,75 +825,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1588,89 +1588,89 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="70" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
-      <c r="F1" s="77"/>
-      <c r="G1" s="77"/>
-      <c r="H1" s="77"/>
-      <c r="I1" s="77"/>
-      <c r="J1" s="77"/>
-      <c r="K1" s="77"/>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
+      <c r="H1" s="70"/>
+      <c r="I1" s="70"/>
+      <c r="J1" s="70"/>
+      <c r="K1" s="70"/>
     </row>
     <row r="2" spans="1:19" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="78" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
-      <c r="J2" s="78"/>
-      <c r="K2" s="78"/>
+      <c r="A2" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="71"/>
+      <c r="C2" s="71"/>
+      <c r="D2" s="71"/>
+      <c r="E2" s="71"/>
+      <c r="F2" s="71"/>
+      <c r="G2" s="71"/>
+      <c r="H2" s="71"/>
+      <c r="I2" s="71"/>
+      <c r="J2" s="71"/>
+      <c r="K2" s="71"/>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A3" s="79" t="s">
+      <c r="A3" s="72" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="79"/>
-      <c r="C3" s="79"/>
-      <c r="D3" s="79"/>
-      <c r="E3" s="79"/>
-      <c r="F3" s="79"/>
-      <c r="G3" s="79"/>
-      <c r="H3" s="79"/>
-      <c r="I3" s="79"/>
-      <c r="J3" s="79"/>
-      <c r="K3" s="79"/>
+      <c r="B3" s="72"/>
+      <c r="C3" s="72"/>
+      <c r="D3" s="72"/>
+      <c r="E3" s="72"/>
+      <c r="F3" s="72"/>
+      <c r="G3" s="72"/>
+      <c r="H3" s="72"/>
+      <c r="I3" s="72"/>
+      <c r="J3" s="72"/>
+      <c r="K3" s="72"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A4" s="79" t="s">
+      <c r="A4" s="72" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="79"/>
-      <c r="C4" s="79"/>
-      <c r="D4" s="79"/>
-      <c r="E4" s="79"/>
-      <c r="F4" s="79"/>
-      <c r="G4" s="79"/>
-      <c r="H4" s="79"/>
-      <c r="I4" s="79"/>
-      <c r="J4" s="79"/>
-      <c r="K4" s="79"/>
+      <c r="B4" s="72"/>
+      <c r="C4" s="72"/>
+      <c r="D4" s="72"/>
+      <c r="E4" s="72"/>
+      <c r="F4" s="72"/>
+      <c r="G4" s="72"/>
+      <c r="H4" s="72"/>
+      <c r="I4" s="72"/>
+      <c r="J4" s="72"/>
+      <c r="K4" s="72"/>
     </row>
     <row r="5" spans="1:19" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A5" s="80" t="s">
+      <c r="A5" s="73" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="80"/>
-      <c r="C5" s="80"/>
-      <c r="D5" s="80"/>
-      <c r="E5" s="80"/>
-      <c r="F5" s="80"/>
-      <c r="G5" s="80"/>
-      <c r="H5" s="80"/>
-      <c r="I5" s="80"/>
-      <c r="J5" s="80"/>
-      <c r="K5" s="80"/>
+      <c r="B5" s="73"/>
+      <c r="C5" s="73"/>
+      <c r="D5" s="73"/>
+      <c r="E5" s="73"/>
+      <c r="F5" s="73"/>
+      <c r="G5" s="73"/>
+      <c r="H5" s="73"/>
+      <c r="I5" s="73"/>
+      <c r="J5" s="73"/>
+      <c r="K5" s="73"/>
     </row>
     <row r="6" spans="1:19" ht="18" x14ac:dyDescent="0.25">
-      <c r="A6" s="67" t="s">
+      <c r="A6" s="74" t="s">
         <v>46</v>
       </c>
-      <c r="B6" s="67"/>
-      <c r="C6" s="67"/>
-      <c r="D6" s="67"/>
-      <c r="E6" s="67"/>
-      <c r="F6" s="67"/>
+      <c r="B6" s="74"/>
+      <c r="C6" s="74"/>
+      <c r="D6" s="74"/>
+      <c r="E6" s="74"/>
+      <c r="F6" s="74"/>
       <c r="G6" s="10"/>
       <c r="H6" s="76" t="s">
         <v>25</v>
@@ -1680,21 +1680,21 @@
       <c r="K6" s="76"/>
     </row>
     <row r="7" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="83" t="s">
+      <c r="A7" s="66" t="s">
         <v>35</v>
       </c>
-      <c r="B7" s="83"/>
-      <c r="C7" s="83"/>
-      <c r="D7" s="83"/>
-      <c r="E7" s="83"/>
-      <c r="F7" s="83"/>
+      <c r="B7" s="66"/>
+      <c r="C7" s="66"/>
+      <c r="D7" s="66"/>
+      <c r="E7" s="66"/>
+      <c r="F7" s="66"/>
       <c r="G7" s="11"/>
-      <c r="H7" s="84" t="s">
+      <c r="H7" s="75" t="s">
         <v>34</v>
       </c>
-      <c r="I7" s="84"/>
-      <c r="J7" s="84"/>
-      <c r="K7" s="84"/>
+      <c r="I7" s="75"/>
+      <c r="J7" s="75"/>
+      <c r="K7" s="75"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
@@ -2337,11 +2337,11 @@
       <c r="B37" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="C37" s="81">
+      <c r="C37" s="64">
         <f>J35</f>
         <v>336113.86499999999</v>
       </c>
-      <c r="D37" s="82"/>
+      <c r="D37" s="65"/>
       <c r="E37" s="9">
         <v>100</v>
       </c>
@@ -2363,21 +2363,21 @@
       <c r="B38" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="C38" s="85">
+      <c r="C38" s="67">
         <v>300000</v>
       </c>
-      <c r="D38" s="86"/>
+      <c r="D38" s="68"/>
       <c r="E38" s="9"/>
     </row>
     <row r="39" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B39" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="C39" s="85">
+      <c r="C39" s="67">
         <f>C38-C41-C42</f>
         <v>285000</v>
       </c>
-      <c r="D39" s="86"/>
+      <c r="D39" s="68"/>
       <c r="E39" s="9">
         <f>C39/C37*100</f>
         <v>84.79269369027665</v>
@@ -2387,11 +2387,11 @@
       <c r="B40" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="C40" s="87">
+      <c r="C40" s="69">
         <f>C37-C39</f>
         <v>51113.864999999991</v>
       </c>
-      <c r="D40" s="87"/>
+      <c r="D40" s="69"/>
       <c r="E40" s="9">
         <f>100-E39</f>
         <v>15.20730630972335</v>
@@ -2401,11 +2401,11 @@
       <c r="B41" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="C41" s="81">
+      <c r="C41" s="64">
         <f>C38*0.03</f>
         <v>9000</v>
       </c>
-      <c r="D41" s="82"/>
+      <c r="D41" s="65"/>
       <c r="E41" s="9">
         <v>3</v>
       </c>
@@ -2414,17 +2414,24 @@
       <c r="B42" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="C42" s="81">
+      <c r="C42" s="64">
         <f>C38*0.02</f>
         <v>6000</v>
       </c>
-      <c r="D42" s="82"/>
+      <c r="D42" s="65"/>
       <c r="E42" s="9">
         <v>2</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="H6:K6"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A4:K4"/>
+    <mergeCell ref="A5:K5"/>
     <mergeCell ref="C41:D41"/>
     <mergeCell ref="C42:D42"/>
     <mergeCell ref="A7:F7"/>
@@ -2433,13 +2440,6 @@
     <mergeCell ref="C38:D38"/>
     <mergeCell ref="C39:D39"/>
     <mergeCell ref="C40:D40"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="H6:K6"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A4:K4"/>
-    <mergeCell ref="A5:K5"/>
   </mergeCells>
   <pageMargins left="0.70866141732283505" right="0.70866141732283505" top="0.74803149606299202" bottom="0.74803149606299202" header="0.31496062992126" footer="0.31496062992126"/>
   <pageSetup paperSize="9" scale="80" orientation="portrait" verticalDpi="1200" r:id="rId1"/>
@@ -2469,90 +2469,90 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="70" t="s">
+      <c r="A1" s="79" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="70"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="70"/>
-      <c r="E1" s="70"/>
-      <c r="F1" s="70"/>
-      <c r="G1" s="70"/>
-      <c r="H1" s="70"/>
-      <c r="I1" s="70"/>
-      <c r="J1" s="70"/>
-      <c r="K1" s="70"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="79"/>
+      <c r="G1" s="79"/>
+      <c r="H1" s="79"/>
+      <c r="I1" s="79"/>
+      <c r="J1" s="79"/>
+      <c r="K1" s="79"/>
     </row>
     <row r="2" spans="1:13" ht="25.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="71" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="71"/>
-      <c r="C2" s="71"/>
-      <c r="D2" s="71"/>
-      <c r="E2" s="71"/>
-      <c r="F2" s="71"/>
-      <c r="G2" s="71"/>
-      <c r="H2" s="71"/>
-      <c r="I2" s="71"/>
-      <c r="J2" s="71"/>
-      <c r="K2" s="71"/>
+      <c r="A2" s="80" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="80"/>
+      <c r="C2" s="80"/>
+      <c r="D2" s="80"/>
+      <c r="E2" s="80"/>
+      <c r="F2" s="80"/>
+      <c r="G2" s="80"/>
+      <c r="H2" s="80"/>
+      <c r="I2" s="80"/>
+      <c r="J2" s="80"/>
+      <c r="K2" s="80"/>
     </row>
     <row r="3" spans="1:13" s="35" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="72" t="s">
+      <c r="A3" s="81" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="72"/>
-      <c r="C3" s="72"/>
-      <c r="D3" s="72"/>
-      <c r="E3" s="72"/>
-      <c r="F3" s="72"/>
-      <c r="G3" s="72"/>
-      <c r="H3" s="72"/>
-      <c r="I3" s="72"/>
-      <c r="J3" s="72"/>
-      <c r="K3" s="72"/>
+      <c r="B3" s="81"/>
+      <c r="C3" s="81"/>
+      <c r="D3" s="81"/>
+      <c r="E3" s="81"/>
+      <c r="F3" s="81"/>
+      <c r="G3" s="81"/>
+      <c r="H3" s="81"/>
+      <c r="I3" s="81"/>
+      <c r="J3" s="81"/>
+      <c r="K3" s="81"/>
     </row>
     <row r="4" spans="1:13" s="35" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="72" t="s">
+      <c r="A4" s="81" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="72"/>
-      <c r="C4" s="72"/>
-      <c r="D4" s="72"/>
-      <c r="E4" s="72"/>
-      <c r="F4" s="72"/>
-      <c r="G4" s="72"/>
-      <c r="H4" s="72"/>
-      <c r="I4" s="72"/>
-      <c r="J4" s="72"/>
-      <c r="K4" s="72"/>
+      <c r="B4" s="81"/>
+      <c r="C4" s="81"/>
+      <c r="D4" s="81"/>
+      <c r="E4" s="81"/>
+      <c r="F4" s="81"/>
+      <c r="G4" s="81"/>
+      <c r="H4" s="81"/>
+      <c r="I4" s="81"/>
+      <c r="J4" s="81"/>
+      <c r="K4" s="81"/>
     </row>
     <row r="5" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A5" s="73" t="s">
+      <c r="A5" s="82" t="s">
         <v>56</v>
       </c>
-      <c r="B5" s="73"/>
-      <c r="C5" s="73"/>
-      <c r="D5" s="73"/>
-      <c r="E5" s="73"/>
-      <c r="F5" s="73"/>
-      <c r="G5" s="73"/>
-      <c r="H5" s="73"/>
-      <c r="I5" s="73"/>
-      <c r="J5" s="73"/>
-      <c r="K5" s="73"/>
+      <c r="B5" s="82"/>
+      <c r="C5" s="82"/>
+      <c r="D5" s="82"/>
+      <c r="E5" s="82"/>
+      <c r="F5" s="82"/>
+      <c r="G5" s="82"/>
+      <c r="H5" s="82"/>
+      <c r="I5" s="82"/>
+      <c r="J5" s="82"/>
+      <c r="K5" s="82"/>
     </row>
     <row r="6" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A6" s="45" t="s">
         <v>57</v>
       </c>
       <c r="B6" s="45"/>
-      <c r="C6" s="74">
+      <c r="C6" s="77">
         <f>F27</f>
         <v>336113.86499999999</v>
       </c>
-      <c r="D6" s="75"/>
+      <c r="D6" s="78"/>
       <c r="E6" s="46"/>
       <c r="F6" s="45"/>
       <c r="G6" s="45"/>
@@ -2560,11 +2560,11 @@
         <v>58</v>
       </c>
       <c r="I6" s="45"/>
-      <c r="J6" s="74">
+      <c r="J6" s="77">
         <f>I27</f>
         <v>208459.4124</v>
       </c>
-      <c r="K6" s="75"/>
+      <c r="K6" s="78"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="47" t="s">
@@ -2573,76 +2573,76 @@
       <c r="B7" s="47"/>
       <c r="C7" s="47"/>
       <c r="D7" s="47"/>
-      <c r="F7" s="65"/>
-      <c r="G7" s="65"/>
-      <c r="I7" s="66" t="s">
+      <c r="F7" s="83"/>
+      <c r="G7" s="83"/>
+      <c r="I7" s="84" t="s">
         <v>60</v>
       </c>
-      <c r="J7" s="66"/>
-      <c r="K7" s="66"/>
+      <c r="J7" s="84"/>
+      <c r="K7" s="84"/>
     </row>
     <row r="8" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A8" s="67" t="s">
+      <c r="A8" s="74" t="s">
         <v>46</v>
       </c>
-      <c r="B8" s="67"/>
-      <c r="C8" s="67"/>
-      <c r="D8" s="67"/>
-      <c r="E8" s="67"/>
-      <c r="F8" s="67"/>
-      <c r="I8" s="68" t="s">
+      <c r="B8" s="74"/>
+      <c r="C8" s="74"/>
+      <c r="D8" s="74"/>
+      <c r="E8" s="74"/>
+      <c r="F8" s="74"/>
+      <c r="I8" s="85" t="s">
         <v>61</v>
       </c>
-      <c r="J8" s="68"/>
-      <c r="K8" s="68"/>
+      <c r="J8" s="85"/>
+      <c r="K8" s="85"/>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A9" s="69" t="str">
+      <c r="A9" s="86" t="str">
         <f>[7]estimate!A7</f>
         <v>Location:- Shankharapur Municipality 1</v>
       </c>
-      <c r="B9" s="69"/>
-      <c r="C9" s="69"/>
-      <c r="D9" s="69"/>
-      <c r="E9" s="69"/>
-      <c r="F9" s="69"/>
-      <c r="I9" s="68" t="s">
+      <c r="B9" s="86"/>
+      <c r="C9" s="86"/>
+      <c r="D9" s="86"/>
+      <c r="E9" s="86"/>
+      <c r="F9" s="86"/>
+      <c r="I9" s="85" t="s">
         <v>71</v>
       </c>
-      <c r="J9" s="68"/>
-      <c r="K9" s="68"/>
+      <c r="J9" s="85"/>
+      <c r="K9" s="85"/>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A11" s="63" t="s">
+      <c r="A11" s="88" t="s">
         <v>62</v>
       </c>
-      <c r="B11" s="63" t="s">
+      <c r="B11" s="88" t="s">
         <v>63</v>
       </c>
-      <c r="C11" s="63" t="s">
+      <c r="C11" s="88" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="64" t="s">
+      <c r="D11" s="89" t="s">
         <v>64</v>
       </c>
-      <c r="E11" s="64"/>
-      <c r="F11" s="64"/>
-      <c r="G11" s="64" t="s">
+      <c r="E11" s="89"/>
+      <c r="F11" s="89"/>
+      <c r="G11" s="89" t="s">
         <v>65</v>
       </c>
-      <c r="H11" s="64"/>
-      <c r="I11" s="64"/>
-      <c r="J11" s="63" t="s">
+      <c r="H11" s="89"/>
+      <c r="I11" s="89"/>
+      <c r="J11" s="88" t="s">
         <v>66</v>
       </c>
-      <c r="K11" s="62" t="s">
+      <c r="K11" s="87" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A12" s="63"/>
-      <c r="B12" s="63"/>
-      <c r="C12" s="63"/>
+      <c r="A12" s="88"/>
+      <c r="B12" s="88"/>
+      <c r="C12" s="88"/>
       <c r="D12" s="48" t="s">
         <v>68</v>
       </c>
@@ -2661,8 +2661,8 @@
       <c r="I12" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="J12" s="63"/>
-      <c r="K12" s="62"/>
+      <c r="J12" s="88"/>
+      <c r="K12" s="87"/>
     </row>
     <row r="13" spans="1:13" s="35" customFormat="1" ht="33" x14ac:dyDescent="0.25">
       <c r="A13" s="49">
@@ -3103,6 +3103,19 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="K11:K12"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="J11:J12"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="I7:K7"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="I8:K8"/>
+    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="I9:K9"/>
     <mergeCell ref="C6:D6"/>
     <mergeCell ref="J6:K6"/>
     <mergeCell ref="A1:K1"/>
@@ -3110,19 +3123,6 @@
     <mergeCell ref="A3:K3"/>
     <mergeCell ref="A4:K4"/>
     <mergeCell ref="A5:K5"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="I7:K7"/>
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="I8:K8"/>
-    <mergeCell ref="A9:F9"/>
-    <mergeCell ref="I9:K9"/>
-    <mergeCell ref="K11:K12"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="D11:F11"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="J11:J12"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3155,89 +3155,89 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="70" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
-      <c r="F1" s="77"/>
-      <c r="G1" s="77"/>
-      <c r="H1" s="77"/>
-      <c r="I1" s="77"/>
-      <c r="J1" s="77"/>
-      <c r="K1" s="77"/>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
+      <c r="H1" s="70"/>
+      <c r="I1" s="70"/>
+      <c r="J1" s="70"/>
+      <c r="K1" s="70"/>
     </row>
     <row r="2" spans="1:11" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="78" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
-      <c r="J2" s="78"/>
-      <c r="K2" s="78"/>
+      <c r="A2" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="71"/>
+      <c r="C2" s="71"/>
+      <c r="D2" s="71"/>
+      <c r="E2" s="71"/>
+      <c r="F2" s="71"/>
+      <c r="G2" s="71"/>
+      <c r="H2" s="71"/>
+      <c r="I2" s="71"/>
+      <c r="J2" s="71"/>
+      <c r="K2" s="71"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="79" t="s">
+      <c r="A3" s="72" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="79"/>
-      <c r="C3" s="79"/>
-      <c r="D3" s="79"/>
-      <c r="E3" s="79"/>
-      <c r="F3" s="79"/>
-      <c r="G3" s="79"/>
-      <c r="H3" s="79"/>
-      <c r="I3" s="79"/>
-      <c r="J3" s="79"/>
-      <c r="K3" s="79"/>
+      <c r="B3" s="72"/>
+      <c r="C3" s="72"/>
+      <c r="D3" s="72"/>
+      <c r="E3" s="72"/>
+      <c r="F3" s="72"/>
+      <c r="G3" s="72"/>
+      <c r="H3" s="72"/>
+      <c r="I3" s="72"/>
+      <c r="J3" s="72"/>
+      <c r="K3" s="72"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="79" t="s">
+      <c r="A4" s="72" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="79"/>
-      <c r="C4" s="79"/>
-      <c r="D4" s="79"/>
-      <c r="E4" s="79"/>
-      <c r="F4" s="79"/>
-      <c r="G4" s="79"/>
-      <c r="H4" s="79"/>
-      <c r="I4" s="79"/>
-      <c r="J4" s="79"/>
-      <c r="K4" s="79"/>
+      <c r="B4" s="72"/>
+      <c r="C4" s="72"/>
+      <c r="D4" s="72"/>
+      <c r="E4" s="72"/>
+      <c r="F4" s="72"/>
+      <c r="G4" s="72"/>
+      <c r="H4" s="72"/>
+      <c r="I4" s="72"/>
+      <c r="J4" s="72"/>
+      <c r="K4" s="72"/>
     </row>
     <row r="5" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A5" s="80" t="s">
+      <c r="A5" s="73" t="s">
         <v>48</v>
       </c>
-      <c r="B5" s="80"/>
-      <c r="C5" s="80"/>
-      <c r="D5" s="80"/>
-      <c r="E5" s="80"/>
-      <c r="F5" s="80"/>
-      <c r="G5" s="80"/>
-      <c r="H5" s="80"/>
-      <c r="I5" s="80"/>
-      <c r="J5" s="80"/>
-      <c r="K5" s="80"/>
+      <c r="B5" s="73"/>
+      <c r="C5" s="73"/>
+      <c r="D5" s="73"/>
+      <c r="E5" s="73"/>
+      <c r="F5" s="73"/>
+      <c r="G5" s="73"/>
+      <c r="H5" s="73"/>
+      <c r="I5" s="73"/>
+      <c r="J5" s="73"/>
+      <c r="K5" s="73"/>
     </row>
     <row r="6" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A6" s="67" t="s">
+      <c r="A6" s="74" t="s">
         <v>46</v>
       </c>
-      <c r="B6" s="67"/>
-      <c r="C6" s="67"/>
-      <c r="D6" s="67"/>
-      <c r="E6" s="67"/>
-      <c r="F6" s="67"/>
+      <c r="B6" s="74"/>
+      <c r="C6" s="74"/>
+      <c r="D6" s="74"/>
+      <c r="E6" s="74"/>
+      <c r="F6" s="74"/>
       <c r="G6" s="10"/>
       <c r="H6" s="76" t="s">
         <v>25</v>
@@ -3247,21 +3247,21 @@
       <c r="K6" s="76"/>
     </row>
     <row r="7" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="83" t="s">
+      <c r="A7" s="66" t="s">
         <v>35</v>
       </c>
-      <c r="B7" s="83"/>
-      <c r="C7" s="83"/>
-      <c r="D7" s="83"/>
-      <c r="E7" s="83"/>
-      <c r="F7" s="83"/>
+      <c r="B7" s="66"/>
+      <c r="C7" s="66"/>
+      <c r="D7" s="66"/>
+      <c r="E7" s="66"/>
+      <c r="F7" s="66"/>
       <c r="G7" s="11"/>
-      <c r="H7" s="84" t="s">
+      <c r="H7" s="75" t="s">
         <v>70</v>
       </c>
-      <c r="I7" s="84"/>
-      <c r="J7" s="84"/>
-      <c r="K7" s="84"/>
+      <c r="I7" s="75"/>
+      <c r="J7" s="75"/>
+      <c r="K7" s="75"/>
     </row>
     <row r="8" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
@@ -4037,11 +4037,11 @@
       <c r="B43" s="27" t="s">
         <v>55</v>
       </c>
-      <c r="C43" s="81">
+      <c r="C43" s="64">
         <f>J41</f>
         <v>208459.4124</v>
       </c>
-      <c r="D43" s="82"/>
+      <c r="D43" s="65"/>
       <c r="E43" s="9">
         <v>100</v>
       </c>
@@ -4056,21 +4056,21 @@
       <c r="B44" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="C44" s="85">
+      <c r="C44" s="67">
         <v>300000</v>
       </c>
-      <c r="D44" s="86"/>
+      <c r="D44" s="68"/>
       <c r="E44" s="9"/>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B45" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="C45" s="85">
+      <c r="C45" s="67">
         <f>84.79%*C43</f>
         <v>176752.73577396001</v>
       </c>
-      <c r="D45" s="86"/>
+      <c r="D45" s="68"/>
       <c r="E45" s="9">
         <f>C45/C43*100</f>
         <v>84.79</v>
@@ -4080,11 +4080,11 @@
       <c r="B46" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="C46" s="87">
+      <c r="C46" s="69">
         <f>C43-C45</f>
         <v>31706.676626039989</v>
       </c>
-      <c r="D46" s="87"/>
+      <c r="D46" s="69"/>
       <c r="E46" s="9">
         <f>100-E45</f>
         <v>15.209999999999994</v>
@@ -4094,11 +4094,11 @@
       <c r="B47" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="C47" s="81">
+      <c r="C47" s="64">
         <f>C44*0.03</f>
         <v>9000</v>
       </c>
-      <c r="D47" s="82"/>
+      <c r="D47" s="65"/>
       <c r="E47" s="9">
         <v>3</v>
       </c>
@@ -4107,24 +4107,17 @@
       <c r="B48" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="C48" s="81">
+      <c r="C48" s="64">
         <f>C44*0.02</f>
         <v>6000</v>
       </c>
-      <c r="D48" s="82"/>
+      <c r="D48" s="65"/>
       <c r="E48" s="9">
         <v>2</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="H6:K6"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A4:K4"/>
-    <mergeCell ref="A5:K5"/>
     <mergeCell ref="C47:D47"/>
     <mergeCell ref="C48:D48"/>
     <mergeCell ref="A7:F7"/>
@@ -4133,6 +4126,13 @@
     <mergeCell ref="C44:D44"/>
     <mergeCell ref="C45:D45"/>
     <mergeCell ref="C46:D46"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="H6:K6"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A4:K4"/>
+    <mergeCell ref="A5:K5"/>
   </mergeCells>
   <phoneticPr fontId="16" type="noConversion"/>
   <pageMargins left="0.70866141732283505" right="0.70866141732283505" top="0.74803149606299202" bottom="0.74803149606299202" header="0.31496062992126" footer="0.31496062992126"/>
@@ -4162,108 +4162,108 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="70" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
-      <c r="F1" s="77"/>
-      <c r="G1" s="77"/>
-      <c r="H1" s="77"/>
-      <c r="I1" s="77"/>
-      <c r="J1" s="77"/>
-      <c r="K1" s="77"/>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
+      <c r="H1" s="70"/>
+      <c r="I1" s="70"/>
+      <c r="J1" s="70"/>
+      <c r="K1" s="70"/>
     </row>
     <row r="2" spans="1:11" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="78" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
-      <c r="J2" s="78"/>
-      <c r="K2" s="78"/>
+      <c r="A2" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="71"/>
+      <c r="C2" s="71"/>
+      <c r="D2" s="71"/>
+      <c r="E2" s="71"/>
+      <c r="F2" s="71"/>
+      <c r="G2" s="71"/>
+      <c r="H2" s="71"/>
+      <c r="I2" s="71"/>
+      <c r="J2" s="71"/>
+      <c r="K2" s="71"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="79" t="s">
+      <c r="A3" s="72" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="79"/>
-      <c r="C3" s="79"/>
-      <c r="D3" s="79"/>
-      <c r="E3" s="79"/>
-      <c r="F3" s="79"/>
-      <c r="G3" s="79"/>
-      <c r="H3" s="79"/>
-      <c r="I3" s="79"/>
-      <c r="J3" s="79"/>
-      <c r="K3" s="79"/>
+      <c r="B3" s="72"/>
+      <c r="C3" s="72"/>
+      <c r="D3" s="72"/>
+      <c r="E3" s="72"/>
+      <c r="F3" s="72"/>
+      <c r="G3" s="72"/>
+      <c r="H3" s="72"/>
+      <c r="I3" s="72"/>
+      <c r="J3" s="72"/>
+      <c r="K3" s="72"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="79" t="s">
+      <c r="A4" s="72" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="79"/>
-      <c r="C4" s="79"/>
-      <c r="D4" s="79"/>
-      <c r="E4" s="79"/>
-      <c r="F4" s="79"/>
-      <c r="G4" s="79"/>
-      <c r="H4" s="79"/>
-      <c r="I4" s="79"/>
-      <c r="J4" s="79"/>
-      <c r="K4" s="79"/>
+      <c r="B4" s="72"/>
+      <c r="C4" s="72"/>
+      <c r="D4" s="72"/>
+      <c r="E4" s="72"/>
+      <c r="F4" s="72"/>
+      <c r="G4" s="72"/>
+      <c r="H4" s="72"/>
+      <c r="I4" s="72"/>
+      <c r="J4" s="72"/>
+      <c r="K4" s="72"/>
     </row>
     <row r="5" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A5" s="80" t="s">
+      <c r="A5" s="73" t="s">
         <v>69</v>
       </c>
-      <c r="B5" s="80"/>
-      <c r="C5" s="80"/>
-      <c r="D5" s="80"/>
-      <c r="E5" s="80"/>
-      <c r="F5" s="80"/>
-      <c r="G5" s="80"/>
-      <c r="H5" s="80"/>
-      <c r="I5" s="80"/>
-      <c r="J5" s="80"/>
-      <c r="K5" s="80"/>
+      <c r="B5" s="73"/>
+      <c r="C5" s="73"/>
+      <c r="D5" s="73"/>
+      <c r="E5" s="73"/>
+      <c r="F5" s="73"/>
+      <c r="G5" s="73"/>
+      <c r="H5" s="73"/>
+      <c r="I5" s="73"/>
+      <c r="J5" s="73"/>
+      <c r="K5" s="73"/>
     </row>
     <row r="6" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A6" s="67" t="s">
+      <c r="A6" s="74" t="s">
         <v>46</v>
       </c>
-      <c r="B6" s="67"/>
-      <c r="C6" s="67"/>
-      <c r="D6" s="67"/>
-      <c r="E6" s="67"/>
-      <c r="F6" s="67"/>
+      <c r="B6" s="74"/>
+      <c r="C6" s="74"/>
+      <c r="D6" s="74"/>
+      <c r="E6" s="74"/>
+      <c r="F6" s="74"/>
       <c r="G6" s="10"/>
-      <c r="I6" s="88"/>
-      <c r="J6" s="88"/>
+      <c r="I6" s="63"/>
+      <c r="J6" s="63"/>
       <c r="K6" s="44" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="83" t="s">
+      <c r="A7" s="66" t="s">
         <v>35</v>
       </c>
-      <c r="B7" s="83"/>
-      <c r="C7" s="83"/>
-      <c r="D7" s="83"/>
-      <c r="E7" s="83"/>
-      <c r="F7" s="83"/>
+      <c r="B7" s="66"/>
+      <c r="C7" s="66"/>
+      <c r="D7" s="66"/>
+      <c r="E7" s="66"/>
+      <c r="F7" s="66"/>
       <c r="G7" s="11"/>
-      <c r="I7" s="89"/>
-      <c r="J7" s="89"/>
+      <c r="I7" s="62"/>
+      <c r="J7" s="62"/>
       <c r="K7" s="43" t="s">
         <v>70</v>
       </c>
@@ -5042,11 +5042,11 @@
       <c r="B43" s="27" t="s">
         <v>55</v>
       </c>
-      <c r="C43" s="81">
+      <c r="C43" s="64">
         <f>J41</f>
         <v>208459.4124</v>
       </c>
-      <c r="D43" s="82"/>
+      <c r="D43" s="65"/>
       <c r="E43" s="9">
         <v>100</v>
       </c>
@@ -5061,21 +5061,21 @@
       <c r="B44" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="C44" s="85">
+      <c r="C44" s="67">
         <v>300000</v>
       </c>
-      <c r="D44" s="86"/>
+      <c r="D44" s="68"/>
       <c r="E44" s="9"/>
     </row>
     <row r="45" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B45" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="C45" s="85">
+      <c r="C45" s="67">
         <f>84.79%*C43</f>
         <v>176752.73577396001</v>
       </c>
-      <c r="D45" s="86"/>
+      <c r="D45" s="68"/>
       <c r="E45" s="9">
         <f>C45/C43*100</f>
         <v>84.79</v>
@@ -5085,11 +5085,11 @@
       <c r="B46" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="C46" s="87">
+      <c r="C46" s="69">
         <f>C43-C45</f>
         <v>31706.676626039989</v>
       </c>
-      <c r="D46" s="87"/>
+      <c r="D46" s="69"/>
       <c r="E46" s="9">
         <f>100-E45</f>
         <v>15.209999999999994</v>
@@ -5099,11 +5099,11 @@
       <c r="B47" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="C47" s="81">
+      <c r="C47" s="64">
         <f>C44*0.03</f>
         <v>9000</v>
       </c>
-      <c r="D47" s="82"/>
+      <c r="D47" s="65"/>
       <c r="E47" s="9">
         <v>3</v>
       </c>
@@ -5112,17 +5112,23 @@
       <c r="B48" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="C48" s="81">
+      <c r="C48" s="64">
         <f>C44*0.02</f>
         <v>6000</v>
       </c>
-      <c r="D48" s="82"/>
+      <c r="D48" s="65"/>
       <c r="E48" s="9">
         <v>2</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A4:K4"/>
+    <mergeCell ref="A5:K5"/>
     <mergeCell ref="C47:D47"/>
     <mergeCell ref="C48:D48"/>
     <mergeCell ref="A7:F7"/>
@@ -5130,12 +5136,6 @@
     <mergeCell ref="C44:D44"/>
     <mergeCell ref="C45:D45"/>
     <mergeCell ref="C46:D46"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A4:K4"/>
-    <mergeCell ref="A5:K5"/>
-    <mergeCell ref="A6:F6"/>
   </mergeCells>
   <pageMargins left="0.70866141732283505" right="0.70866141732283505" top="0.74803149606299202" bottom="0.74803149606299202" header="0.31496062992126" footer="0.31496062992126"/>
   <pageSetup paperSize="9" scale="95" orientation="portrait" verticalDpi="1200" r:id="rId1"/>
@@ -5166,89 +5166,89 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="70" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
-      <c r="F1" s="77"/>
-      <c r="G1" s="77"/>
-      <c r="H1" s="77"/>
-      <c r="I1" s="77"/>
-      <c r="J1" s="77"/>
-      <c r="K1" s="77"/>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
+      <c r="H1" s="70"/>
+      <c r="I1" s="70"/>
+      <c r="J1" s="70"/>
+      <c r="K1" s="70"/>
     </row>
     <row r="2" spans="1:19" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="78" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
-      <c r="J2" s="78"/>
-      <c r="K2" s="78"/>
+      <c r="A2" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="71"/>
+      <c r="C2" s="71"/>
+      <c r="D2" s="71"/>
+      <c r="E2" s="71"/>
+      <c r="F2" s="71"/>
+      <c r="G2" s="71"/>
+      <c r="H2" s="71"/>
+      <c r="I2" s="71"/>
+      <c r="J2" s="71"/>
+      <c r="K2" s="71"/>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A3" s="79" t="s">
+      <c r="A3" s="72" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="79"/>
-      <c r="C3" s="79"/>
-      <c r="D3" s="79"/>
-      <c r="E3" s="79"/>
-      <c r="F3" s="79"/>
-      <c r="G3" s="79"/>
-      <c r="H3" s="79"/>
-      <c r="I3" s="79"/>
-      <c r="J3" s="79"/>
-      <c r="K3" s="79"/>
+      <c r="B3" s="72"/>
+      <c r="C3" s="72"/>
+      <c r="D3" s="72"/>
+      <c r="E3" s="72"/>
+      <c r="F3" s="72"/>
+      <c r="G3" s="72"/>
+      <c r="H3" s="72"/>
+      <c r="I3" s="72"/>
+      <c r="J3" s="72"/>
+      <c r="K3" s="72"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A4" s="79" t="s">
+      <c r="A4" s="72" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="79"/>
-      <c r="C4" s="79"/>
-      <c r="D4" s="79"/>
-      <c r="E4" s="79"/>
-      <c r="F4" s="79"/>
-      <c r="G4" s="79"/>
-      <c r="H4" s="79"/>
-      <c r="I4" s="79"/>
-      <c r="J4" s="79"/>
-      <c r="K4" s="79"/>
+      <c r="B4" s="72"/>
+      <c r="C4" s="72"/>
+      <c r="D4" s="72"/>
+      <c r="E4" s="72"/>
+      <c r="F4" s="72"/>
+      <c r="G4" s="72"/>
+      <c r="H4" s="72"/>
+      <c r="I4" s="72"/>
+      <c r="J4" s="72"/>
+      <c r="K4" s="72"/>
     </row>
     <row r="5" spans="1:19" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A5" s="80" t="s">
+      <c r="A5" s="73" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="80"/>
-      <c r="C5" s="80"/>
-      <c r="D5" s="80"/>
-      <c r="E5" s="80"/>
-      <c r="F5" s="80"/>
-      <c r="G5" s="80"/>
-      <c r="H5" s="80"/>
-      <c r="I5" s="80"/>
-      <c r="J5" s="80"/>
-      <c r="K5" s="80"/>
+      <c r="B5" s="73"/>
+      <c r="C5" s="73"/>
+      <c r="D5" s="73"/>
+      <c r="E5" s="73"/>
+      <c r="F5" s="73"/>
+      <c r="G5" s="73"/>
+      <c r="H5" s="73"/>
+      <c r="I5" s="73"/>
+      <c r="J5" s="73"/>
+      <c r="K5" s="73"/>
     </row>
     <row r="6" spans="1:19" ht="18" x14ac:dyDescent="0.25">
-      <c r="A6" s="67" t="s">
+      <c r="A6" s="74" t="s">
         <v>46</v>
       </c>
-      <c r="B6" s="67"/>
-      <c r="C6" s="67"/>
-      <c r="D6" s="67"/>
-      <c r="E6" s="67"/>
-      <c r="F6" s="67"/>
+      <c r="B6" s="74"/>
+      <c r="C6" s="74"/>
+      <c r="D6" s="74"/>
+      <c r="E6" s="74"/>
+      <c r="F6" s="74"/>
       <c r="G6" s="10"/>
       <c r="H6" s="76" t="s">
         <v>25</v>
@@ -5258,21 +5258,21 @@
       <c r="K6" s="76"/>
     </row>
     <row r="7" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="83" t="s">
+      <c r="A7" s="66" t="s">
         <v>35</v>
       </c>
-      <c r="B7" s="83"/>
-      <c r="C7" s="83"/>
-      <c r="D7" s="83"/>
-      <c r="E7" s="83"/>
-      <c r="F7" s="83"/>
+      <c r="B7" s="66"/>
+      <c r="C7" s="66"/>
+      <c r="D7" s="66"/>
+      <c r="E7" s="66"/>
+      <c r="F7" s="66"/>
       <c r="G7" s="11"/>
-      <c r="H7" s="84" t="s">
+      <c r="H7" s="75" t="s">
         <v>34</v>
       </c>
-      <c r="I7" s="84"/>
-      <c r="J7" s="84"/>
-      <c r="K7" s="84"/>
+      <c r="I7" s="75"/>
+      <c r="J7" s="75"/>
+      <c r="K7" s="75"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
@@ -5897,11 +5897,11 @@
       <c r="B36" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="C36" s="81">
+      <c r="C36" s="64">
         <f>J34</f>
         <v>335761.30499999999</v>
       </c>
-      <c r="D36" s="82"/>
+      <c r="D36" s="65"/>
       <c r="E36" s="9">
         <v>100</v>
       </c>
@@ -5923,21 +5923,21 @@
       <c r="B37" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="C37" s="85">
+      <c r="C37" s="67">
         <v>300000</v>
       </c>
-      <c r="D37" s="86"/>
+      <c r="D37" s="68"/>
       <c r="E37" s="9"/>
     </row>
     <row r="38" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B38" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="C38" s="85">
+      <c r="C38" s="67">
         <f>C37-C40-C41</f>
         <v>285000</v>
       </c>
-      <c r="D38" s="86"/>
+      <c r="D38" s="68"/>
       <c r="E38" s="9">
         <f>C38/C36*100</f>
         <v>84.881728703073762</v>
@@ -5947,11 +5947,11 @@
       <c r="B39" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="C39" s="87">
+      <c r="C39" s="69">
         <f>C36-C38</f>
         <v>50761.304999999993</v>
       </c>
-      <c r="D39" s="87"/>
+      <c r="D39" s="69"/>
       <c r="E39" s="9">
         <f>100-E38</f>
         <v>15.118271296926238</v>
@@ -5961,11 +5961,11 @@
       <c r="B40" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="C40" s="81">
+      <c r="C40" s="64">
         <f>C37*0.03</f>
         <v>9000</v>
       </c>
-      <c r="D40" s="82"/>
+      <c r="D40" s="65"/>
       <c r="E40" s="9">
         <v>3</v>
       </c>
@@ -5974,24 +5974,17 @@
       <c r="B41" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="C41" s="81">
+      <c r="C41" s="64">
         <f>C37*0.02</f>
         <v>6000</v>
       </c>
-      <c r="D41" s="82"/>
+      <c r="D41" s="65"/>
       <c r="E41" s="9">
         <v>2</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="H6:K6"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A4:K4"/>
-    <mergeCell ref="A5:K5"/>
     <mergeCell ref="C40:D40"/>
     <mergeCell ref="C41:D41"/>
     <mergeCell ref="A7:F7"/>
@@ -6000,6 +5993,13 @@
     <mergeCell ref="C37:D37"/>
     <mergeCell ref="C38:D38"/>
     <mergeCell ref="C39:D39"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="H6:K6"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A4:K4"/>
+    <mergeCell ref="A5:K5"/>
   </mergeCells>
   <pageMargins left="0.70866141732283505" right="0.70866141732283505" top="0.74803149606299202" bottom="0.74803149606299202" header="0.31496062992126" footer="0.31496062992126"/>
   <pageSetup paperSize="9" scale="80" orientation="portrait" verticalDpi="1200" r:id="rId1"/>
